--- a/AAII_Financials/Quarterly/CBNK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CBNK_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/CBNK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CBNK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
   <si>
     <t>CBNK</t>
   </si>
@@ -656,226 +656,239 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>47000</v>
+      </c>
+      <c r="F8" s="3">
         <v>47700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>45100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>43400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>41300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>38300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>36600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>34400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>33800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>33500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>29300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>26600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>28300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>25200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>22000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>21700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>21200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>22400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>20300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>18300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>18200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>17400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>33400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>16700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>14700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>15000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>14200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>12800</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -963,8 +976,14 @@
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1052,8 +1071,14 @@
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1085,8 +1110,10 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1174,8 +1201,14 @@
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1263,8 +1296,14 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1352,8 +1391,14 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1441,8 +1486,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,186 +1522,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>14800</v>
+      </c>
+      <c r="F17" s="3">
         <v>13200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>12600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>10600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>8500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>3200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2400</v>
-      </c>
-      <c r="M17" s="3">
-        <v>2600</v>
-      </c>
-      <c r="N17" s="3">
-        <v>2700</v>
       </c>
       <c r="O17" s="3">
         <v>2600</v>
       </c>
       <c r="P17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>2600</v>
+      </c>
+      <c r="R17" s="3">
         <v>3200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>3400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>4100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>5300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>5200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>4400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>3700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>3800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>3500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>6100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>2800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>2900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>2700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>2500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>2300</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>32200</v>
+      </c>
+      <c r="F18" s="3">
         <v>34500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>32500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>32800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>32800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>35400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>33400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>32400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>31600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>31100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>26800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>23900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>25700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>22100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>18600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>17600</v>
-      </c>
-      <c r="S18" s="3">
-        <v>15900</v>
-      </c>
-      <c r="T18" s="3">
-        <v>17200</v>
       </c>
       <c r="U18" s="3">
         <v>15900</v>
       </c>
       <c r="V18" s="3">
+        <v>17200</v>
+      </c>
+      <c r="W18" s="3">
+        <v>15900</v>
+      </c>
+      <c r="X18" s="3">
         <v>14600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>14400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>14000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>27300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>13900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>11800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>12300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>11700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>10500</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1682,186 +1747,200 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-21700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-22900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-20200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-21100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-20900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-18800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-18800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-17900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-16000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-13700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-11800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-12700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-12100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-13600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-9300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-11100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-10300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-10200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-9600</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-9600</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-18700</v>
       </c>
       <c r="Z20" s="3">
         <v>-9600</v>
       </c>
       <c r="AA20" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-10400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-7300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-7500</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>11300</v>
+      </c>
+      <c r="F21" s="3">
         <v>12900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>9600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>12700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>10900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>14800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>15000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>14000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>13200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>15100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>13500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>12600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>12500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>12100</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>6900</v>
-      </c>
-      <c r="R21" s="3">
-        <v>4500</v>
       </c>
       <c r="S21" s="3">
         <v>6900</v>
       </c>
       <c r="T21" s="3">
+        <v>4500</v>
+      </c>
+      <c r="U21" s="3">
+        <v>6900</v>
+      </c>
+      <c r="V21" s="3">
         <v>6400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>5900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>4700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>5100</v>
-      </c>
-      <c r="X21" s="3">
-        <v>4600</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>9200</v>
       </c>
       <c r="Z21" s="3">
         <v>4600</v>
       </c>
       <c r="AA21" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AC21" s="3">
         <v>1700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>5200</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF21" s="3">
         <v>3300</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1949,186 +2028,204 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>11200</v>
+      </c>
+      <c r="F23" s="3">
         <v>12800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>9600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>12700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>11600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>14400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>14600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>13600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>13700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>15100</v>
-      </c>
-      <c r="M23" s="3">
-        <v>13000</v>
-      </c>
-      <c r="N23" s="3">
-        <v>12100</v>
       </c>
       <c r="O23" s="3">
         <v>13000</v>
       </c>
       <c r="P23" s="3">
+        <v>12100</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>13000</v>
+      </c>
+      <c r="R23" s="3">
         <v>11600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>6500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>4000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>6700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>6100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>5600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>4400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>4800</v>
-      </c>
-      <c r="X23" s="3">
-        <v>4300</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>8700</v>
       </c>
       <c r="Z23" s="3">
         <v>4300</v>
       </c>
       <c r="AA23" s="3">
+        <v>8700</v>
+      </c>
+      <c r="AB23" s="3">
+        <v>4300</v>
+      </c>
+      <c r="AC23" s="3">
         <v>1400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>5000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>4700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>3000</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F24" s="3">
         <v>3000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>2300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>2900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>2700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>3300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>3100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>3400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>3500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>3900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>3400</v>
-      </c>
-      <c r="N24" s="3">
-        <v>3100</v>
-      </c>
-      <c r="O24" s="3">
-        <v>3300</v>
       </c>
       <c r="P24" s="3">
         <v>3100</v>
       </c>
       <c r="Q24" s="3">
+        <v>3300</v>
+      </c>
+      <c r="R24" s="3">
+        <v>3100</v>
+      </c>
+      <c r="S24" s="3">
         <v>1800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>1100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>1600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>1600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>1500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>1100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>1300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>1200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>2500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>1400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>1900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>1800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>1200</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,186 +2313,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F26" s="3">
         <v>9800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>7300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>9700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>9000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>11100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>11500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>10200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>10200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>11200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>9600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>9000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>9700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>8400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>4800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>2900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>5100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>4500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>4000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>3300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>3500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>3100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>6100</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>3000</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>700</v>
       </c>
       <c r="AB26" s="3">
         <v>3000</v>
       </c>
       <c r="AC26" s="3">
+        <v>700</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AE26" s="3">
         <v>2900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>1900</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F27" s="3">
         <v>9800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>7300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>9700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>9000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>11100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>11500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>10200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>10200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>11200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>9600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>9000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>9700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>8400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>4800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>2900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>5100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>4500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>4000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>3300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>3500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>3100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>6100</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>3000</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>700</v>
       </c>
       <c r="AB27" s="3">
         <v>3000</v>
       </c>
       <c r="AC27" s="3">
+        <v>700</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AE27" s="3">
         <v>2900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>1900</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,8 +2598,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2539,41 +2660,47 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>3</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2788,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,186 +2883,204 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>21000</v>
+      </c>
+      <c r="F32" s="3">
         <v>21700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>22900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>20200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>21100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>20900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>18800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>18800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>17900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>16000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>13700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>11800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>12700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>10500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>12100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>13600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>9300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>11100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>10300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>10200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>9600</v>
-      </c>
-      <c r="X32" s="3">
-        <v>9600</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>18700</v>
       </c>
       <c r="Z32" s="3">
         <v>9600</v>
       </c>
       <c r="AA32" s="3">
+        <v>18700</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>9600</v>
+      </c>
+      <c r="AC32" s="3">
         <v>10400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>7300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>7000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>7500</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F33" s="3">
         <v>9800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>7300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>9700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>9000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>11100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>11500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>10200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>10200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>11200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>9600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>9000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>9700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>8400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>4800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>2900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>5100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>4500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>4000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>3300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>3500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>3100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>6100</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>3000</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>-600</v>
       </c>
       <c r="AB33" s="3">
         <v>3000</v>
       </c>
       <c r="AC33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AD33" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AE33" s="3">
         <v>2900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>1900</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,191 +3168,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F35" s="3">
         <v>9800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>7300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>9700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>9000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>11100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>11500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>10200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>10200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>11200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>9600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>9000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>9700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>8400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>4800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>2900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>5100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>4500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>4000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>3300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>3500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>3100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>6100</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>3000</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>-600</v>
       </c>
       <c r="AB35" s="3">
         <v>3000</v>
       </c>
       <c r="AC35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AD35" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AE35" s="3">
         <v>2900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>1900</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3402,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,86 +3437,88 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>14500</v>
+      </c>
+      <c r="F41" s="3">
         <v>13800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>18600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>14500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>20000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>14800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>14800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>15000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>42900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>23700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>19700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>22700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>18500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>20100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>15600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>9600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>10500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>11100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>12300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>11600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>10400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>11000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>9800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>9600</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3355,86 +3528,92 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>72800</v>
+      </c>
+      <c r="E42" s="3">
+        <v>39500</v>
+      </c>
+      <c r="F42" s="3">
         <v>132400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>100700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>125900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>60500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>22500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>236400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>299100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>140700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>300600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>289200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>295600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>128500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>185400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>184100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>165300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>104300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>44000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>67300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>26700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>24300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>29700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>58900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>35500</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3444,8 +3623,14 @@
       <c r="AE42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3533,8 +3718,14 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3622,8 +3813,14 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3711,8 +3908,14 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3800,8 +4003,14 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3889,85 +4098,91 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F48" s="3">
         <v>5300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>5500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>5400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3200</v>
-      </c>
-      <c r="I48" s="3">
-        <v>3300</v>
-      </c>
-      <c r="J48" s="3">
-        <v>3000</v>
       </c>
       <c r="K48" s="3">
         <v>3300</v>
       </c>
       <c r="L48" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N48" s="3">
         <v>3700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>4100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>4000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>4500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>5000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>5500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>5600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>12200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>6700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>7200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>7700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>3000</v>
-      </c>
-      <c r="X48" s="3">
-        <v>2800</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>2800</v>
       </c>
       <c r="Z48" s="3">
         <v>2800</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
+      <c r="AA48" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AB48" s="3">
+        <v>2800</v>
       </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
@@ -3978,8 +4193,14 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4067,8 +4288,14 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4383,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,86 +4478,92 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>12300</v>
+      </c>
+      <c r="F52" s="3">
         <v>13600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>13600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>12900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>13800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>14000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>12900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>12400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>9800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>7200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>7400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>7400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>6800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>3600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>3600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>4000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>4300</v>
-      </c>
-      <c r="T52" s="3">
-        <v>3600</v>
-      </c>
-      <c r="U52" s="3">
-        <v>3500</v>
       </c>
       <c r="V52" s="3">
         <v>3600</v>
       </c>
       <c r="W52" s="3">
-        <v>3700</v>
+        <v>3500</v>
       </c>
       <c r="X52" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="Y52" s="3">
         <v>3700</v>
       </c>
       <c r="Z52" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AA52" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AB52" s="3">
         <v>3600</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4334,8 +4573,14 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,86 +4668,92 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2324200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2226200</v>
+      </c>
+      <c r="F54" s="3">
         <v>2272500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2227900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2245300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>2123700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>2009400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>2154800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>2122500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>2055300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2169600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>2151900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2091900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1876600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1879000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1822400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1507800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1427600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1311400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1234200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1123800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1105100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1072900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1067800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1017600</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4512,8 +4763,14 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4802,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,86 +4837,88 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F57" s="3">
         <v>5200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>500</v>
-      </c>
-      <c r="I57" s="3">
-        <v>300</v>
       </c>
       <c r="J57" s="3">
         <v>500</v>
       </c>
       <c r="K57" s="3">
+        <v>300</v>
+      </c>
+      <c r="L57" s="3">
         <v>500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
+        <v>500</v>
+      </c>
+      <c r="N57" s="3">
         <v>800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>2100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>2000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>2000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>1700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>1400</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4667,8 +4928,14 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4676,7 +4943,7 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -4756,85 +5023,91 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F59" s="3">
         <v>4000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>4300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>4100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>3000</v>
-      </c>
-      <c r="M59" s="3">
-        <v>3400</v>
-      </c>
-      <c r="N59" s="3">
-        <v>3100</v>
       </c>
       <c r="O59" s="3">
         <v>3400</v>
       </c>
       <c r="P59" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="R59" s="3">
         <v>3800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>4200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>4000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>4300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>4600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>4900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>5100</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>0</v>
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC59" s="3">
         <v>0</v>
@@ -4845,8 +5118,14 @@
       <c r="AE59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4934,8 +5213,14 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4973,19 +5258,19 @@
         <v>12100</v>
       </c>
       <c r="O61" s="3">
+        <v>12100</v>
+      </c>
+      <c r="P61" s="3">
+        <v>12100</v>
+      </c>
+      <c r="Q61" s="3">
         <v>14000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>17500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>17400</v>
-      </c>
-      <c r="R61" s="3">
-        <v>15400</v>
-      </c>
-      <c r="S61" s="3">
-        <v>15400</v>
       </c>
       <c r="T61" s="3">
         <v>15400</v>
@@ -5003,7 +5288,7 @@
         <v>15400</v>
       </c>
       <c r="Y61" s="3">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="Z61" s="3">
         <v>15400</v>
@@ -5012,7 +5297,7 @@
         <v>0</v>
       </c>
       <c r="AB61" s="3">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="AC61" s="3">
         <v>0</v>
@@ -5023,8 +5308,14 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5112,8 +5403,14 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5498,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5593,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,86 +5688,92 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2064800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1971300</v>
+      </c>
+      <c r="F66" s="3">
         <v>2029600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1990400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2010800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1899600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1795400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1947500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1921000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1857400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1980500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1974600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1924800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1717300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1729700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1680300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1371800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1294300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1183600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1111000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1005200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>990500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>966200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>980800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>934200</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5468,8 +5783,14 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5822,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5913,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +6008,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5768,8 +6103,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,86 +6198,92 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>218700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>213300</v>
+      </c>
+      <c r="F72" s="3">
         <v>206000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>197500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>191100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>182400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>174900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>164800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>153900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>144500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>135900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>125400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>115800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>106900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>97600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>89200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>84400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>81600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>77100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>72900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>68900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>65700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>62500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>59300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>56200</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5946,8 +6293,14 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6388,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6483,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,86 +6578,92 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>259500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>254900</v>
+      </c>
+      <c r="F76" s="3">
         <v>242900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>237400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>234500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>224000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>214000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>207300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>201500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>197900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>189100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>177200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>167000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>159300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>149400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>142100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>136100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>133300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>127800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>123100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>118600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>114600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>106700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>87000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>83400</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6302,8 +6673,14 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,191 +6768,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F81" s="3">
         <v>9800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>7300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>9700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>9000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>11100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>11500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>10200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>10200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>11200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>9600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>9000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>9700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>8400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>4800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>2900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>5100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>4500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>4000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>3300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>3500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>3100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>6100</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>3000</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>-600</v>
       </c>
       <c r="AB81" s="3">
         <v>3000</v>
       </c>
       <c r="AC81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AD81" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AE81" s="3">
         <v>2900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>1900</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,8 +7002,10 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6622,46 +7019,46 @@
         <v>100</v>
       </c>
       <c r="G83" s="3">
+        <v>100</v>
+      </c>
+      <c r="H83" s="3">
+        <v>100</v>
+      </c>
+      <c r="I83" s="3">
         <v>-700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>-500</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
         <v>500</v>
-      </c>
-      <c r="N83" s="3">
-        <v>500</v>
-      </c>
-      <c r="O83" s="3">
-        <v>-600</v>
       </c>
       <c r="P83" s="3">
         <v>500</v>
       </c>
       <c r="Q83" s="3">
-        <v>400</v>
+        <v>-600</v>
       </c>
       <c r="R83" s="3">
         <v>500</v>
       </c>
       <c r="S83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="T83" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="U83" s="3">
         <v>300</v>
@@ -6673,31 +7070,37 @@
         <v>300</v>
       </c>
       <c r="X83" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z83" s="3">
         <v>200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>300</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD83" s="3">
         <v>200</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +7188,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7283,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7378,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7473,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,97 +7568,109 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F89" s="3">
         <v>22500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>8400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>10400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>6000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>15800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>20300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>9200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>29500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>26400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>21500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>54600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>41300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-30100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>3100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>8200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-14800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-21500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>10400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>2800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>15100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>12900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>6800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>4700</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,97 +7702,105 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-2300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3">
         <v>100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W91" s="3">
-        <v>-700</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-300</v>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y91" s="3">
         <v>-700</v>
       </c>
       <c r="Z91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-300</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7888,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,97 +7983,109 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-57600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-39100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-26300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-6700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-58700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-68000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-77700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-108800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>56100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-45900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-14500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-85300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-92600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-86000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-34000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-249500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-16000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-57300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-81700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-42500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-6400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-43400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-33800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-32000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-16700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-32300</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,8 +8117,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7661,29 +8128,29 @@
         <v>-1100</v>
       </c>
       <c r="E96" s="3">
-        <v>-800</v>
+        <v>-1100</v>
       </c>
       <c r="F96" s="3">
-        <v>-900</v>
+        <v>-1100</v>
       </c>
       <c r="G96" s="3">
         <v>-800</v>
       </c>
       <c r="H96" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I96" s="3">
         <v>-800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K96" s="3">
         <v>-700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-700</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -7741,8 +8208,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8303,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8398,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,97 +8493,109 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>92300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-59200</v>
+      </c>
+      <c r="F100" s="3">
         <v>30600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-22700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>108300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>105300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-151900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>25600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>65100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-124300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>3400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>54400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>209100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-14000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>48700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>304400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>73000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>109700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>72100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>105200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>8300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>27000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>3000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>33300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-10600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>22700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>16600</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8186,93 +8683,105 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-92200</v>
+      </c>
+      <c r="F102" s="3">
         <v>26800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-21000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>60000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>43400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-213800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-62900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>130400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-140600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>15300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-9400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>171100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-58600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>5800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>24800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>60000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>59700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-24500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>41200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>3600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-6000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-28000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>16400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-9700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>12700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-10900</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CBNK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CBNK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
   <si>
     <t>CBNK</t>
   </si>
@@ -656,239 +656,246 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>50600</v>
+      </c>
+      <c r="E8" s="3">
         <v>48400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>47000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>47700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>45100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>43400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>41300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>38300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>36600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>34400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>33800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>33500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>29300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>26600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>28300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>25200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>22000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>21700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>21200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>22400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>20300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>18300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>18200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>17400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>33400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>16700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>14700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>15000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>14200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>12800</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -982,8 +989,11 @@
       <c r="AG9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1077,8 +1087,11 @@
       <c r="AG10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1112,8 +1125,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1207,8 +1221,11 @@
       <c r="AG12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,8 +1319,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1397,8 +1417,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1492,8 +1515,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1550,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E17" s="3">
         <v>16200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>10600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2300</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>32200</v>
+        <v>33500</v>
       </c>
       <c r="E18" s="3">
         <v>32200</v>
       </c>
       <c r="F18" s="3">
+        <v>32200</v>
+      </c>
+      <c r="G18" s="3">
         <v>34500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>32500</v>
-      </c>
-      <c r="H18" s="3">
-        <v>32800</v>
       </c>
       <c r="I18" s="3">
         <v>32800</v>
       </c>
       <c r="J18" s="3">
+        <v>32800</v>
+      </c>
+      <c r="K18" s="3">
         <v>35400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>33400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>32400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>31600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>31100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>26800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>23900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>25700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>22100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>18600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>17600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>15900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>17200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>15900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>14600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>14400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>14000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>27300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>13900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>11800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>12300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>11700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>10500</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,198 +1782,205 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-23500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-21000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-21700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-22900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-20200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-21100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-20900</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-18800</v>
       </c>
       <c r="L20" s="3">
         <v>-18800</v>
       </c>
       <c r="M20" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="N20" s="3">
         <v>-17900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-16000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-13700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-12700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-10500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-12100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-13600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-9300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-11100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-10300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-10200</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-9600</v>
       </c>
       <c r="Z20" s="3">
         <v>-9600</v>
       </c>
       <c r="AA20" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-18700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-9600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-10400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-7300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-7000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-7500</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E21" s="3">
         <v>8700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>12900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>12700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>10900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>14800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>15000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>14000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>13200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>15100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>13500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>12600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>12500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>12100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>6900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>6900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>6400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>5900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>9200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>5200</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG21" s="3">
         <v>3300</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2034,198 +2074,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E23" s="3">
         <v>8600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>11200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>12800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>9600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>12700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>11600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>14400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>14600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>13600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>13700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>15100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>13000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>12100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>13000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>11600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>5600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>8700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>5000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3000</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E24" s="3">
         <v>2100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1100</v>
-      </c>
-      <c r="U24" s="3">
-        <v>1600</v>
       </c>
       <c r="V24" s="3">
         <v>1600</v>
       </c>
       <c r="W24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="X24" s="3">
         <v>1500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1200</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2368,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E26" s="3">
         <v>6600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>9000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>9800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>9700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>9000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>11100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>11500</v>
-      </c>
-      <c r="L26" s="3">
-        <v>10200</v>
       </c>
       <c r="M26" s="3">
         <v>10200</v>
       </c>
       <c r="N26" s="3">
+        <v>10200</v>
+      </c>
+      <c r="O26" s="3">
         <v>11200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>9600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>9000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>9700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>8400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>6100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1900</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E27" s="3">
         <v>6600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>9000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>9800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>9700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>9000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>11100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>11500</v>
-      </c>
-      <c r="L27" s="3">
-        <v>10200</v>
       </c>
       <c r="M27" s="3">
         <v>10200</v>
       </c>
       <c r="N27" s="3">
+        <v>10200</v>
+      </c>
+      <c r="O27" s="3">
         <v>11200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>9600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>9000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>9700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>8400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>6100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1900</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2662,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2666,17 +2727,17 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>3</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>3</v>
+      <c r="Y29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>3</v>
@@ -2684,12 +2745,12 @@
       <c r="AB29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>3</v>
       </c>
@@ -2699,8 +2760,11 @@
       <c r="AG29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2858,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,198 +2956,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E32" s="3">
         <v>23500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>21000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>21700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>22900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>20200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>21100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>20900</v>
-      </c>
-      <c r="K32" s="3">
-        <v>18800</v>
       </c>
       <c r="L32" s="3">
         <v>18800</v>
       </c>
       <c r="M32" s="3">
+        <v>18800</v>
+      </c>
+      <c r="N32" s="3">
         <v>17900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>16000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>13700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>11800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>12700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>10500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>12100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>13600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>9300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>11100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>10300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>10200</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>9600</v>
       </c>
       <c r="Z32" s="3">
         <v>9600</v>
       </c>
       <c r="AA32" s="3">
+        <v>9600</v>
+      </c>
+      <c r="AB32" s="3">
         <v>18700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>9600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>10400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>7300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>7000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>7500</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E33" s="3">
         <v>6600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>9000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>9800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>9700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>9000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>11100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>11500</v>
-      </c>
-      <c r="L33" s="3">
-        <v>10200</v>
       </c>
       <c r="M33" s="3">
         <v>10200</v>
       </c>
       <c r="N33" s="3">
+        <v>10200</v>
+      </c>
+      <c r="O33" s="3">
         <v>11200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>9600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>9000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>9700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>8400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>6100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1900</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3250,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E35" s="3">
         <v>6600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>9000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>9800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>9700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>9000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>11100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>11500</v>
-      </c>
-      <c r="L35" s="3">
-        <v>10200</v>
       </c>
       <c r="M35" s="3">
         <v>10200</v>
       </c>
       <c r="N35" s="3">
+        <v>10200</v>
+      </c>
+      <c r="O35" s="3">
         <v>11200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>9600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>9000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>9700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>8400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>6100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1900</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3489,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,89 +3525,90 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E41" s="3">
         <v>12400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>13800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>18600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>14500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>20000</v>
-      </c>
-      <c r="J41" s="3">
-        <v>14800</v>
       </c>
       <c r="K41" s="3">
         <v>14800</v>
       </c>
       <c r="L41" s="3">
+        <v>14800</v>
+      </c>
+      <c r="M41" s="3">
         <v>15000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>42900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>23700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>19700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>22700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>18500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>20100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>15600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>11100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>12300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>11600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>10400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>11000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>9800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>9600</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3534,89 +3621,92 @@
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>117200</v>
+      </c>
+      <c r="E42" s="3">
         <v>72800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>39500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>132400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>100700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>125900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>60500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>22500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>236400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>299100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>140700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>300600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>289200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>295600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>128500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>185400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>184100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>165300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>104300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>44000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>67300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>26700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>24300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>29700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>58900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>35500</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3629,8 +3719,11 @@
       <c r="AG42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3724,8 +3817,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3819,8 +3915,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3914,8 +4013,11 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4009,8 +4111,11 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4104,79 +4209,82 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E48" s="3">
         <v>4500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3000</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>2800</v>
       </c>
       <c r="AA48" s="3">
         <v>2800</v>
@@ -4184,8 +4292,8 @@
       <c r="AB48" s="3">
         <v>2800</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>3</v>
+      <c r="AC48" s="3">
+        <v>2800</v>
       </c>
       <c r="AD48" s="3" t="s">
         <v>3</v>
@@ -4199,8 +4307,11 @@
       <c r="AG48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4294,8 +4405,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4503,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,76 +4601,79 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>12300</v>
+        <v>12200</v>
       </c>
       <c r="E52" s="3">
         <v>12300</v>
       </c>
       <c r="F52" s="3">
-        <v>13600</v>
+        <v>12300</v>
       </c>
       <c r="G52" s="3">
         <v>13600</v>
       </c>
       <c r="H52" s="3">
+        <v>13600</v>
+      </c>
+      <c r="I52" s="3">
         <v>12900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7200</v>
-      </c>
-      <c r="O52" s="3">
-        <v>7400</v>
       </c>
       <c r="P52" s="3">
         <v>7400</v>
       </c>
       <c r="Q52" s="3">
+        <v>7400</v>
+      </c>
+      <c r="R52" s="3">
         <v>6800</v>
-      </c>
-      <c r="R52" s="3">
-        <v>3600</v>
       </c>
       <c r="S52" s="3">
         <v>3600</v>
       </c>
       <c r="T52" s="3">
+        <v>3600</v>
+      </c>
+      <c r="U52" s="3">
         <v>4000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3600</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>3700</v>
       </c>
       <c r="Z52" s="3">
         <v>3700</v>
@@ -4562,11 +4682,11 @@
         <v>3700</v>
       </c>
       <c r="AB52" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AC52" s="3">
         <v>3600</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4579,8 +4699,11 @@
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,89 +4797,92 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2438600</v>
+      </c>
+      <c r="E54" s="3">
         <v>2324200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2226200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2272500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2227900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2245300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2123700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2009400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2154800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2122500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2055300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2169600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2151900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2091900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1876600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1879000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1822400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1507800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1427600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1311400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1234200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1123800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1105100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1072900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1067800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1017600</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4769,8 +4895,11 @@
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4933,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,89 +4969,90 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E57" s="3">
         <v>6000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>300</v>
-      </c>
-      <c r="L57" s="3">
-        <v>500</v>
       </c>
       <c r="M57" s="3">
         <v>500</v>
       </c>
       <c r="N57" s="3">
+        <v>500</v>
+      </c>
+      <c r="O57" s="3">
         <v>800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2100</v>
-      </c>
-      <c r="W57" s="3">
-        <v>2000</v>
       </c>
       <c r="X57" s="3">
         <v>2000</v>
       </c>
       <c r="Y57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Z57" s="3">
         <v>1600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1400</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4934,8 +5065,11 @@
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4943,11 +5077,11 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>15000</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
@@ -5029,77 +5163,80 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E59" s="3">
         <v>3500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5100</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5109,8 +5246,8 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC59" s="3">
-        <v>0</v>
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD59" s="3">
         <v>0</v>
@@ -5124,8 +5261,11 @@
       <c r="AG59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5219,8 +5359,11 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5264,16 +5407,16 @@
         <v>12100</v>
       </c>
       <c r="Q61" s="3">
+        <v>12100</v>
+      </c>
+      <c r="R61" s="3">
         <v>14000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>17500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>17400</v>
-      </c>
-      <c r="T61" s="3">
-        <v>15400</v>
       </c>
       <c r="U61" s="3">
         <v>15400</v>
@@ -5294,14 +5437,14 @@
         <v>15400</v>
       </c>
       <c r="AA61" s="3">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>15400</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -5314,8 +5457,11 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5409,8 +5555,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5653,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5751,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,89 +5849,92 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2170700</v>
+      </c>
+      <c r="E66" s="3">
         <v>2064800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1971300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2029600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1990400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2010800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1899600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1795400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1947500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1921000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1857400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1980500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1974600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1924800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1717300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1729700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1680300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1371800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1294300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1183600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1111000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1005200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>990500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>966200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>980800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>934200</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5789,8 +5947,11 @@
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5985,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6081,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6179,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6277,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,89 +6375,92 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>225800</v>
+      </c>
+      <c r="E72" s="3">
         <v>218700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>213300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>206000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>197500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>191100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>182400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>174900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>164800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>153900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>144500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>135900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>125400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>115800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>106900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>97600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>89200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>84400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>81600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>77100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>72900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>68900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>65700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>62500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>59300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>56200</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6299,8 +6473,11 @@
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6571,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6669,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,89 +6767,92 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>267900</v>
+      </c>
+      <c r="E76" s="3">
         <v>259500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>254900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>242900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>237400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>234500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>224000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>214000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>207300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>201500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>197900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>189100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>177200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>167000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>159300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>149400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>142100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>136100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>133300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>127800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>123100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>118600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>114600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>106700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>87000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>83400</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6679,8 +6865,11 @@
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6963,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E81" s="3">
         <v>6600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>9000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>9800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>9700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>9000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>11100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>11500</v>
-      </c>
-      <c r="L81" s="3">
-        <v>10200</v>
       </c>
       <c r="M81" s="3">
         <v>10200</v>
       </c>
       <c r="N81" s="3">
+        <v>10200</v>
+      </c>
+      <c r="O81" s="3">
         <v>11200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>9600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>9000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>9700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>8400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>6100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1900</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,8 +7202,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7025,43 +7224,43 @@
         <v>100</v>
       </c>
       <c r="I83" s="3">
+        <v>100</v>
+      </c>
+      <c r="J83" s="3">
         <v>-700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>300</v>
-      </c>
-      <c r="K83" s="3">
-        <v>400</v>
       </c>
       <c r="L83" s="3">
         <v>400</v>
       </c>
       <c r="M83" s="3">
+        <v>400</v>
+      </c>
+      <c r="N83" s="3">
         <v>-500</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="P83" s="3">
         <v>500</v>
       </c>
       <c r="Q83" s="3">
+        <v>500</v>
+      </c>
+      <c r="R83" s="3">
         <v>-600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>500</v>
-      </c>
-      <c r="U83" s="3">
-        <v>300</v>
       </c>
       <c r="V83" s="3">
         <v>300</v>
@@ -7076,31 +7275,34 @@
         <v>300</v>
       </c>
       <c r="Z83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA83" s="3">
         <v>200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>300</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD83" s="3">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE83" s="3">
         <v>200</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7396,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7494,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7592,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7690,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +7788,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>22500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>8400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>10400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>15800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>20300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>9200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>29500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>26400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>21500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>54600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>41300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-30100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>8200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-14800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-21500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>10400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>15100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>12900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>6800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>4700</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,65 +7924,66 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-2300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-700</v>
       </c>
       <c r="K91" s="3">
         <v>-700</v>
       </c>
       <c r="L91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3">
         <v>100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7772,35 +7993,38 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-700</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-400</v>
       </c>
       <c r="AC91" s="3">
         <v>-400</v>
       </c>
       <c r="AD91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-300</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8118,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,103 +8216,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-65500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-57600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-39100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-26300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-58700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-68000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-77700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-108800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>56100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-45900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-85300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-92600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-86000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-34000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-249500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-16000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-57300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-81700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-42500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-43400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-33800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-32000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-12000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-16700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-32300</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8352,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8134,25 +8368,25 @@
         <v>-1100</v>
       </c>
       <c r="G96" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="H96" s="3">
         <v>-800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-900</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-800</v>
       </c>
       <c r="J96" s="3">
         <v>-800</v>
       </c>
       <c r="K96" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="L96" s="3">
         <v>-700</v>
       </c>
       <c r="M96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -8214,8 +8448,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8546,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8644,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,103 +8742,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>103900</v>
+      </c>
+      <c r="E100" s="3">
         <v>92300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-59200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>30600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-22700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>108300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>105300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-151900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>25600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>65100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-124300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>54400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>209100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-14000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>48700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>304400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>73000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>109700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>72100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>105200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>8300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>27000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>3000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>33300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-10600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>22700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>16600</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8689,99 +8938,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>51300</v>
+      </c>
+      <c r="E102" s="3">
         <v>31200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-92200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>26800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-21000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>60000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>43400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-213800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-62900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>130400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-140600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>15300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-9400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>171100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-58600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>24800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>60000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>59700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-24500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>41200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-28000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>16400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-9700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>12700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-10900</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CBNK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CBNK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
   <si>
     <t>CBNK</t>
   </si>
@@ -656,246 +656,253 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>50600</v>
+        <v>41200</v>
       </c>
       <c r="E8" s="3">
-        <v>48400</v>
+        <v>40400</v>
       </c>
       <c r="F8" s="3">
-        <v>47000</v>
+        <v>38100</v>
       </c>
       <c r="G8" s="3">
-        <v>47700</v>
+        <v>38100</v>
       </c>
       <c r="H8" s="3">
-        <v>45100</v>
+        <v>40800</v>
       </c>
       <c r="I8" s="3">
-        <v>43400</v>
+        <v>39200</v>
       </c>
       <c r="J8" s="3">
+        <v>38900</v>
+      </c>
+      <c r="K8" s="3">
         <v>41300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>38300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>36600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>34400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>33800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>33500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>29300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>26600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>28300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>25200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>22000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>21700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>21200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>22400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>20300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>18300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>18200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>17400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>33400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>16700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>14700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>15000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>14200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>12800</v>
       </c>
-      <c r="AH8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -992,31 +999,34 @@
       <c r="AH9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>40400</v>
+      </c>
+      <c r="F10" s="3">
+        <v>38100</v>
+      </c>
+      <c r="G10" s="3">
+        <v>38100</v>
+      </c>
+      <c r="H10" s="3">
+        <v>40800</v>
+      </c>
+      <c r="I10" s="3">
+        <v>39200</v>
+      </c>
+      <c r="J10" s="3">
+        <v>38900</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -1090,8 +1100,11 @@
       <c r="AH10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1126,8 +1139,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1224,8 +1238,11 @@
       <c r="AH12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1322,31 +1339,34 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>700</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1420,31 +1440,34 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1518,8 +1541,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1551,204 +1577,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>17100</v>
+        <v>29200</v>
       </c>
       <c r="E17" s="3">
-        <v>16200</v>
+        <v>29400</v>
       </c>
       <c r="F17" s="3">
-        <v>14800</v>
+        <v>28800</v>
       </c>
       <c r="G17" s="3">
-        <v>13200</v>
+        <v>26900</v>
       </c>
       <c r="H17" s="3">
-        <v>12600</v>
+        <v>28000</v>
       </c>
       <c r="I17" s="3">
-        <v>10600</v>
+        <v>29600</v>
       </c>
       <c r="J17" s="3">
+        <v>26200</v>
+      </c>
+      <c r="K17" s="3">
         <v>8500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2300</v>
       </c>
-      <c r="AH17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>33500</v>
+        <v>12000</v>
       </c>
       <c r="E18" s="3">
-        <v>32200</v>
+        <v>11000</v>
       </c>
       <c r="F18" s="3">
-        <v>32200</v>
+        <v>9300</v>
       </c>
       <c r="G18" s="3">
-        <v>34500</v>
+        <v>11200</v>
       </c>
       <c r="H18" s="3">
-        <v>32500</v>
+        <v>12800</v>
       </c>
       <c r="I18" s="3">
+        <v>9600</v>
+      </c>
+      <c r="J18" s="3">
+        <v>12700</v>
+      </c>
+      <c r="K18" s="3">
         <v>32800</v>
       </c>
-      <c r="J18" s="3">
-        <v>32800</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>35400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>33400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>32400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>31600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>31100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>26800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>23900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>25700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>22100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>18600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>17600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>15900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>17200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>15900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>14600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>14400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>14000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>27300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>13900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>11800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>12300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>11700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>10500</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1783,227 +1816,234 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-22600</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-23500</v>
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F20" s="3">
-        <v>-21000</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>-21700</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>-22900</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-20200</v>
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-21100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-20900</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-18800</v>
       </c>
       <c r="M20" s="3">
         <v>-18800</v>
       </c>
       <c r="N20" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="O20" s="3">
         <v>-17900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-16000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-13700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-11800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-12700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-10500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-12100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-13600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-9300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-11100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-10300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-10200</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-9600</v>
       </c>
       <c r="AA20" s="3">
         <v>-9600</v>
       </c>
       <c r="AB20" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-18700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-9600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-10400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-7300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-7000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-7500</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>11000</v>
+        <v>12100</v>
       </c>
       <c r="E21" s="3">
-        <v>8700</v>
+        <v>11100</v>
       </c>
       <c r="F21" s="3">
+        <v>9400</v>
+      </c>
+      <c r="G21" s="3">
         <v>11300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>12900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>9600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>12700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>10900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>14800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>15000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>14000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>13200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>15100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>13500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>12600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>12500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>12100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>6900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>6900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>6400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>5900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>5100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>9200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>5200</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH21" s="3">
         <v>3300</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2077,204 +2117,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E23" s="3">
         <v>10900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>8600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>11200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>12800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>9600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>12700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>11600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>14400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>14600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>13600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>13700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>15100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>13000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>12100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>13000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>11600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>8700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>5000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3000</v>
       </c>
-      <c r="AH23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E24" s="3">
         <v>2700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1100</v>
-      </c>
-      <c r="V24" s="3">
-        <v>1600</v>
       </c>
       <c r="W24" s="3">
         <v>1600</v>
       </c>
       <c r="X24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Y24" s="3">
         <v>1500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1200</v>
       </c>
-      <c r="AH24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2371,204 +2420,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E26" s="3">
         <v>8200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>9000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>9800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>9700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>9000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>11100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>11500</v>
-      </c>
-      <c r="M26" s="3">
-        <v>10200</v>
       </c>
       <c r="N26" s="3">
         <v>10200</v>
       </c>
       <c r="O26" s="3">
+        <v>10200</v>
+      </c>
+      <c r="P26" s="3">
         <v>11200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>9600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>9000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>9700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>8400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>6100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1900</v>
       </c>
-      <c r="AH26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E27" s="3">
         <v>8200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>9000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>9800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>9700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>9000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>11100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>11500</v>
-      </c>
-      <c r="M27" s="3">
-        <v>10200</v>
       </c>
       <c r="N27" s="3">
         <v>10200</v>
       </c>
       <c r="O27" s="3">
+        <v>10200</v>
+      </c>
+      <c r="P27" s="3">
         <v>11200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>9600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>9000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>9700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>8400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>6100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1900</v>
       </c>
-      <c r="AH27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2665,8 +2723,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2730,17 +2791,17 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>3</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>3</v>
+      <c r="Z29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>3</v>
@@ -2748,12 +2809,12 @@
       <c r="AC29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>3</v>
       </c>
@@ -2763,8 +2824,11 @@
       <c r="AH29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2861,8 +2925,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2959,204 +3026,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>22600</v>
-      </c>
-      <c r="E32" s="3">
-        <v>23500</v>
+        <v>0</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F32" s="3">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>21700</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>22900</v>
-      </c>
-      <c r="I32" s="3">
-        <v>20200</v>
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>21100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>20900</v>
-      </c>
-      <c r="L32" s="3">
-        <v>18800</v>
       </c>
       <c r="M32" s="3">
         <v>18800</v>
       </c>
       <c r="N32" s="3">
+        <v>18800</v>
+      </c>
+      <c r="O32" s="3">
         <v>17900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>16000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>13700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>11800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>12700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>10500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>12100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>13600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>9300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>11100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>10300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>10200</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>9600</v>
       </c>
       <c r="AA32" s="3">
         <v>9600</v>
       </c>
       <c r="AB32" s="3">
+        <v>9600</v>
+      </c>
+      <c r="AC32" s="3">
         <v>18700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>9600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>10400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>7300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>7000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>7500</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E33" s="3">
         <v>8200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>9000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>9800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>9700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>9000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>11100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>11500</v>
-      </c>
-      <c r="M33" s="3">
-        <v>10200</v>
       </c>
       <c r="N33" s="3">
         <v>10200</v>
       </c>
       <c r="O33" s="3">
+        <v>10200</v>
+      </c>
+      <c r="P33" s="3">
         <v>11200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>9600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>9000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>9700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>8400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>6100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1900</v>
       </c>
-      <c r="AH33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3253,209 +3329,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E35" s="3">
         <v>8200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>9000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>9800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>9700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>9000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>11100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>11500</v>
-      </c>
-      <c r="M35" s="3">
-        <v>10200</v>
       </c>
       <c r="N35" s="3">
         <v>10200</v>
       </c>
       <c r="O35" s="3">
+        <v>10200</v>
+      </c>
+      <c r="P35" s="3">
         <v>11200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>9600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>9000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>9700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>8400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>6100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1900</v>
       </c>
-      <c r="AH35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3490,8 +3575,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3526,92 +3612,93 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>19300</v>
+        <v>156700</v>
       </c>
       <c r="E41" s="3">
-        <v>12400</v>
+        <v>136500</v>
       </c>
       <c r="F41" s="3">
-        <v>14500</v>
+        <v>85200</v>
       </c>
       <c r="G41" s="3">
-        <v>13800</v>
+        <v>54000</v>
       </c>
       <c r="H41" s="3">
-        <v>18600</v>
+        <v>146200</v>
       </c>
       <c r="I41" s="3">
-        <v>14500</v>
+        <v>119300</v>
       </c>
       <c r="J41" s="3">
+        <v>140400</v>
+      </c>
+      <c r="K41" s="3">
         <v>20000</v>
-      </c>
-      <c r="K41" s="3">
-        <v>14800</v>
       </c>
       <c r="L41" s="3">
         <v>14800</v>
       </c>
       <c r="M41" s="3">
+        <v>14800</v>
+      </c>
+      <c r="N41" s="3">
         <v>15000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>42900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>23700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>19700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>22700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>18500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>20100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>15600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>11100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>12300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>11600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>10400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>11000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>9800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>9600</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3624,92 +3711,95 @@
       <c r="AH41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>117200</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>72800</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>39500</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>132400</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>100700</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>125900</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>60500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>22500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>236400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>299100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>140700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>300600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>289200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>295600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>128500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>185400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>184100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>165300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>104300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>44000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>67300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>26700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>24300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>29700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>58900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>35500</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3722,31 +3812,34 @@
       <c r="AH42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+        <v>11600</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3820,31 +3913,34 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3918,31 +4014,34 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>12500</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>12200</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>12300</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>11500</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>11200</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4016,31 +4115,34 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>189300</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>169200</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>119400</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>72900</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>162200</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>139600</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4114,31 +4216,34 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>208700</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>207900</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>202300</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>208300</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>206100</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>208500</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>255800</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4212,82 +4317,85 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E48" s="3">
         <v>5600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3000</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>2800</v>
       </c>
       <c r="AB48" s="3">
         <v>2800</v>
@@ -4295,8 +4403,8 @@
       <c r="AC48" s="3">
         <v>2800</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>3</v>
+      <c r="AD48" s="3">
+        <v>2800</v>
       </c>
       <c r="AE48" s="3" t="s">
         <v>3</v>
@@ -4310,8 +4418,11 @@
       <c r="AH48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4408,8 +4519,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4506,8 +4620,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4604,79 +4721,82 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>12200</v>
+        <v>70500</v>
       </c>
       <c r="E52" s="3">
-        <v>12300</v>
+        <v>53000</v>
       </c>
       <c r="F52" s="3">
-        <v>12300</v>
+        <v>50600</v>
       </c>
       <c r="G52" s="3">
-        <v>13600</v>
+        <v>52900</v>
       </c>
       <c r="H52" s="3">
-        <v>13600</v>
+        <v>50900</v>
       </c>
       <c r="I52" s="3">
+        <v>50000</v>
+      </c>
+      <c r="J52" s="3">
+        <v>49300</v>
+      </c>
+      <c r="K52" s="3">
+        <v>13800</v>
+      </c>
+      <c r="L52" s="3">
+        <v>14000</v>
+      </c>
+      <c r="M52" s="3">
         <v>12900</v>
       </c>
-      <c r="J52" s="3">
-        <v>13800</v>
-      </c>
-      <c r="K52" s="3">
-        <v>14000</v>
-      </c>
-      <c r="L52" s="3">
-        <v>12900</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7200</v>
-      </c>
-      <c r="P52" s="3">
-        <v>7400</v>
       </c>
       <c r="Q52" s="3">
         <v>7400</v>
       </c>
       <c r="R52" s="3">
+        <v>7400</v>
+      </c>
+      <c r="S52" s="3">
         <v>6800</v>
-      </c>
-      <c r="S52" s="3">
-        <v>3600</v>
       </c>
       <c r="T52" s="3">
         <v>3600</v>
       </c>
       <c r="U52" s="3">
+        <v>3600</v>
+      </c>
+      <c r="V52" s="3">
         <v>4000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3600</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>3700</v>
       </c>
       <c r="AA52" s="3">
         <v>3700</v>
@@ -4685,11 +4805,11 @@
         <v>3700</v>
       </c>
       <c r="AC52" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AD52" s="3">
         <v>3600</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4702,8 +4822,11 @@
       <c r="AH52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4800,92 +4923,95 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2560800</v>
+      </c>
+      <c r="E54" s="3">
         <v>2438600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2324200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2226200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2272500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2227900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2245300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2123700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2009400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2154800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2122500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2055300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2169600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2151900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2091900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1876600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1879000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1822400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1507800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1427600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1311400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1234200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1123800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1105100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1072900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1067800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1017600</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4898,8 +5024,11 @@
       <c r="AH54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4934,8 +5063,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4970,92 +5100,93 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>6600</v>
+        <v>2186200</v>
       </c>
       <c r="E57" s="3">
-        <v>6000</v>
+        <v>2100400</v>
       </c>
       <c r="F57" s="3">
-        <v>5600</v>
+        <v>2005700</v>
       </c>
       <c r="G57" s="3">
-        <v>5200</v>
+        <v>1896000</v>
       </c>
       <c r="H57" s="3">
-        <v>3000</v>
+        <v>1968000</v>
       </c>
       <c r="I57" s="3">
-        <v>2000</v>
+        <v>1934400</v>
       </c>
       <c r="J57" s="3">
+        <v>1944400</v>
+      </c>
+      <c r="K57" s="3">
         <v>1000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>300</v>
-      </c>
-      <c r="M57" s="3">
-        <v>500</v>
       </c>
       <c r="N57" s="3">
         <v>500</v>
       </c>
       <c r="O57" s="3">
+        <v>500</v>
+      </c>
+      <c r="P57" s="3">
         <v>800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2100</v>
-      </c>
-      <c r="X57" s="3">
-        <v>2000</v>
       </c>
       <c r="Y57" s="3">
         <v>2000</v>
       </c>
       <c r="Z57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AA57" s="3">
         <v>1600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1400</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5068,31 +5199,34 @@
       <c r="AH57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F58" s="3">
-        <v>15000</v>
+        <v>800</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>10900</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5166,80 +5300,83 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>4400</v>
-      </c>
-      <c r="E59" s="3">
-        <v>3500</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="L59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="M59" s="3">
+        <v>2900</v>
+      </c>
+      <c r="N59" s="3">
+        <v>2500</v>
+      </c>
+      <c r="O59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="P59" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="R59" s="3">
+        <v>3100</v>
+      </c>
+      <c r="S59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="T59" s="3">
         <v>3800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="U59" s="3">
+        <v>4200</v>
+      </c>
+      <c r="V59" s="3">
         <v>4000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="W59" s="3">
         <v>4300</v>
       </c>
-      <c r="I59" s="3">
-        <v>4100</v>
-      </c>
-      <c r="J59" s="3">
-        <v>2400</v>
-      </c>
-      <c r="K59" s="3">
-        <v>2700</v>
-      </c>
-      <c r="L59" s="3">
-        <v>2900</v>
-      </c>
-      <c r="M59" s="3">
-        <v>2500</v>
-      </c>
-      <c r="N59" s="3">
-        <v>2700</v>
-      </c>
-      <c r="O59" s="3">
-        <v>3000</v>
-      </c>
-      <c r="P59" s="3">
-        <v>3400</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>3100</v>
-      </c>
-      <c r="R59" s="3">
-        <v>3400</v>
-      </c>
-      <c r="S59" s="3">
-        <v>3800</v>
-      </c>
-      <c r="T59" s="3">
-        <v>4200</v>
-      </c>
-      <c r="U59" s="3">
-        <v>4000</v>
-      </c>
-      <c r="V59" s="3">
-        <v>4300</v>
-      </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5100</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5249,8 +5386,8 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD59" s="3">
-        <v>0</v>
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE59" s="3">
         <v>0</v>
@@ -5264,31 +5401,34 @@
       <c r="AH59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>2195000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>2107600</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>2012500</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>1917700</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>1973500</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>1938100</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>1957300</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5362,31 +5502,34 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>12100</v>
+        <v>68200</v>
       </c>
       <c r="E61" s="3">
-        <v>12100</v>
+        <v>47900</v>
       </c>
       <c r="F61" s="3">
-        <v>12100</v>
+        <v>36700</v>
       </c>
       <c r="G61" s="3">
-        <v>12100</v>
+        <v>36700</v>
       </c>
       <c r="H61" s="3">
-        <v>12100</v>
+        <v>37700</v>
       </c>
       <c r="I61" s="3">
-        <v>12100</v>
+        <v>37700</v>
       </c>
       <c r="J61" s="3">
-        <v>12100</v>
+        <v>37200</v>
       </c>
       <c r="K61" s="3">
         <v>12100</v>
@@ -5410,16 +5553,16 @@
         <v>12100</v>
       </c>
       <c r="R61" s="3">
+        <v>12100</v>
+      </c>
+      <c r="S61" s="3">
         <v>14000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>17500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>17400</v>
-      </c>
-      <c r="U61" s="3">
-        <v>15400</v>
       </c>
       <c r="V61" s="3">
         <v>15400</v>
@@ -5440,14 +5583,14 @@
         <v>15400</v>
       </c>
       <c r="AB61" s="3">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>15400</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
@@ -5460,31 +5603,34 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>17500</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>15200</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>15500</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>16900</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>18400</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>14700</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>16300</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -5558,8 +5704,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5656,8 +5805,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5754,8 +5906,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5852,92 +6007,95 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2280700</v>
+      </c>
+      <c r="E66" s="3">
         <v>2170700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2064800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1971300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2029600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1990400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2010800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1899600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1795400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1947500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1921000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1857400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1980500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1974600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1924800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1717300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1729700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1680300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1371800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1294300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1183600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1111000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1005200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>990500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>966200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>980800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>934200</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5950,8 +6108,11 @@
       <c r="AH66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5986,8 +6147,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6084,8 +6246,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6182,8 +6347,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6280,8 +6448,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6378,92 +6549,95 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>233000</v>
+      </c>
+      <c r="E72" s="3">
         <v>225800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>218700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>213300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>206000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>197500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>191100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>182400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>174900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>164800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>153900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>144500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>135900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>125400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>115800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>106900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>97600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>89200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>84400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>81600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>77100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>72900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>68900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>65700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>62500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>59300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>56200</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6476,8 +6650,11 @@
       <c r="AH72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6574,8 +6751,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6672,8 +6852,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6770,92 +6953,95 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>280100</v>
+      </c>
+      <c r="E76" s="3">
         <v>267900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>259500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>254900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>242900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>237400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>234500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>224000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>214000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>207300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>201500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>197900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>189100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>177200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>167000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>159300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>149400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>142100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>136100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>133300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>127800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>123100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>118600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>114600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>106700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>87000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>83400</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6868,8 +7054,11 @@
       <c r="AH76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6966,209 +7155,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E81" s="3">
         <v>8200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>9000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>9800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>9700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>9000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>11100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>11500</v>
-      </c>
-      <c r="M81" s="3">
-        <v>10200</v>
       </c>
       <c r="N81" s="3">
         <v>10200</v>
       </c>
       <c r="O81" s="3">
+        <v>10200</v>
+      </c>
+      <c r="P81" s="3">
         <v>11200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>9600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>9000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>9700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>8400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>6100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1900</v>
       </c>
-      <c r="AH81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7203,67 +7401,68 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G83" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H83" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I83" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="J83" s="3">
+        <v>400</v>
+      </c>
+      <c r="K83" s="3">
         <v>-700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>300</v>
-      </c>
-      <c r="L83" s="3">
-        <v>400</v>
       </c>
       <c r="M83" s="3">
         <v>400</v>
       </c>
       <c r="N83" s="3">
+        <v>400</v>
+      </c>
+      <c r="O83" s="3">
         <v>-500</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
       <c r="P83" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="Q83" s="3">
         <v>500</v>
       </c>
       <c r="R83" s="3">
+        <v>500</v>
+      </c>
+      <c r="S83" s="3">
         <v>-600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>500</v>
-      </c>
-      <c r="V83" s="3">
-        <v>300</v>
       </c>
       <c r="W83" s="3">
         <v>300</v>
@@ -7278,31 +7477,34 @@
         <v>300</v>
       </c>
       <c r="AA83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB83" s="3">
         <v>200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>300</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF83" s="3">
         <v>200</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7399,8 +7601,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7497,8 +7702,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7595,8 +7803,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7693,8 +7904,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7791,106 +8005,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E89" s="3">
         <v>12900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>22500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>10400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>15800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>20300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>9200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>29500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>26400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>21500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>54600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>41300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-8900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-30100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>8200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-14800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-21500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>10400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>15100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>12900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>6800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>4700</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7925,68 +8145,69 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
-        <v>-400</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3">
+        <v>400</v>
+      </c>
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-2300</v>
       </c>
-      <c r="I91" s="3">
-        <v>-500</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-700</v>
       </c>
       <c r="L91" s="3">
         <v>-700</v>
       </c>
       <c r="M91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R91" s="3">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3">
         <v>100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7996,35 +8217,38 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-700</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>-400</v>
       </c>
       <c r="AD91" s="3">
         <v>-400</v>
       </c>
       <c r="AE91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-300</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8121,8 +8345,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8219,106 +8446,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-83700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-65500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-57600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-39100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-26300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-58700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-68000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-77700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-108800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>56100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-45900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-14500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-85300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-92600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-86000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-34000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-249500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-16000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-57300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-81700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-42500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-6400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-43400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-33800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-32000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-12000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-16700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-32300</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8353,43 +8586,44 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1100</v>
+        <v>1400</v>
       </c>
       <c r="E96" s="3">
-        <v>-1100</v>
+        <v>1100</v>
       </c>
       <c r="F96" s="3">
-        <v>-1100</v>
+        <v>1100</v>
       </c>
       <c r="G96" s="3">
-        <v>-1100</v>
+        <v>1100</v>
       </c>
       <c r="H96" s="3">
-        <v>-800</v>
+        <v>1100</v>
       </c>
       <c r="I96" s="3">
-        <v>-900</v>
+        <v>800</v>
       </c>
       <c r="J96" s="3">
-        <v>-800</v>
+        <v>900</v>
       </c>
       <c r="K96" s="3">
         <v>-800</v>
       </c>
       <c r="L96" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="M96" s="3">
         <v>-700</v>
       </c>
       <c r="N96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -8451,8 +8685,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8549,8 +8786,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8647,8 +8887,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8745,129 +8988,135 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>104400</v>
+      </c>
+      <c r="E100" s="3">
         <v>103900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>92300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-59200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>30600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-22700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>108300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>105300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-151900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>25600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>65100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-124300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>54400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>209100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-14000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>48700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>304400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>73000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>109700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>72100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>105200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>8300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>27000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>3000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>33300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-10600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>22700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>16600</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -8941,102 +9190,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E102" s="3">
         <v>51300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>31200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-92200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>26800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-21000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>60000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>43400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-213800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-62900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>130400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-140600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>15300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>171100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-58600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>24800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>60000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>59700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-24500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>41200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>3600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-28000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>16400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-9700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>12700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-10900</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CBNK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CBNK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
   <si>
     <t>CBNK</t>
   </si>
@@ -656,253 +656,259 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2" t="s">
+      <c r="AJ7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>50900</v>
+      </c>
+      <c r="E8" s="3">
         <v>41200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>40400</v>
-      </c>
-      <c r="F8" s="3">
-        <v>38100</v>
       </c>
       <c r="G8" s="3">
         <v>38100</v>
       </c>
       <c r="H8" s="3">
+        <v>38100</v>
+      </c>
+      <c r="I8" s="3">
         <v>40800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>39200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>38900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>41300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>38300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>36600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>34400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>33800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>33500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>29300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>26600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>28300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>25200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>22000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>21700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>21200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>22400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>20300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>18300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>18200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>17400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>33400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>16700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>14700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>15000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>14200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>12800</v>
       </c>
-      <c r="AI8" s="3" t="s">
+      <c r="AJ8" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1002,35 +1008,38 @@
       <c r="AI9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>50900</v>
+      </c>
+      <c r="E10" s="3">
         <v>41200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>40400</v>
-      </c>
-      <c r="F10" s="3">
-        <v>38100</v>
       </c>
       <c r="G10" s="3">
         <v>38100</v>
       </c>
       <c r="H10" s="3">
+        <v>38100</v>
+      </c>
+      <c r="I10" s="3">
         <v>40800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>39200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>38900</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1103,8 +1112,11 @@
       <c r="AI10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1140,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1241,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1342,23 +1358,26 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E14" s="3">
         <v>500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>700</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1368,8 +1387,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1443,13 +1462,16 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="E15" s="3">
         <v>100</v>
@@ -1470,7 +1492,7 @@
         <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1544,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1578,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E17" s="3">
         <v>29200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>29400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>28800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>26900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>28000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>29600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>26200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2300</v>
       </c>
-      <c r="AI17" s="3" t="s">
+      <c r="AJ17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E18" s="3">
         <v>12000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>11000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>9300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>11200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>12800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>9600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>12700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>32800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>35400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>33400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>32400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>31600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>31100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>26800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>23900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>25700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>22100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>18600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>17600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>15900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>17200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>15900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>14600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>14400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>14000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>27300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>13900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>11800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>12300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>11700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>10500</v>
       </c>
-      <c r="AI18" s="3" t="s">
+      <c r="AJ18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1817,19 +1849,20 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
@@ -1837,190 +1870,196 @@
       <c r="H20" s="3">
         <v>0</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-21100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-20900</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-18800</v>
       </c>
       <c r="N20" s="3">
         <v>-18800</v>
       </c>
       <c r="O20" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="P20" s="3">
         <v>-17900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-13700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-11800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-12700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-10500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-12100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-13600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-9300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-11100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-10300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-10200</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>-9600</v>
       </c>
       <c r="AB20" s="3">
         <v>-9600</v>
       </c>
       <c r="AC20" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-18700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-9600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-10400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-7300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-7000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-7500</v>
       </c>
-      <c r="AI20" s="3" t="s">
+      <c r="AJ20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E21" s="3">
         <v>12100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>9400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>11300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>12900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>12700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>10900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>14800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>15000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>14000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>13200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>15100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>13500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>12600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>12500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>12100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>6900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>6900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>5100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>9200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>5200</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI21" s="3">
         <v>3300</v>
       </c>
-      <c r="AI21" s="3" t="s">
+      <c r="AJ21" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2045,8 +2084,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2120,210 +2159,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E23" s="3">
         <v>11500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>10900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>8600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>11200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>12800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>9600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>12700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>11600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>14400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>14600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>13600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>13700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>15100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>13000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>12100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>13000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>11600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>5600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>8700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>5000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>4700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3000</v>
       </c>
-      <c r="AI23" s="3" t="s">
+      <c r="AJ23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E24" s="3">
         <v>2800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1100</v>
-      </c>
-      <c r="W24" s="3">
-        <v>1600</v>
       </c>
       <c r="X24" s="3">
         <v>1600</v>
       </c>
       <c r="Y24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Z24" s="3">
         <v>1500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1200</v>
       </c>
-      <c r="AI24" s="3" t="s">
+      <c r="AJ24" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2423,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E26" s="3">
         <v>8700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>9000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>9800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>9700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>9000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>11100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>11500</v>
-      </c>
-      <c r="N26" s="3">
-        <v>10200</v>
       </c>
       <c r="O26" s="3">
         <v>10200</v>
       </c>
       <c r="P26" s="3">
+        <v>10200</v>
+      </c>
+      <c r="Q26" s="3">
         <v>11200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>9600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>9000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>9700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>8400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>6100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1900</v>
       </c>
-      <c r="AI26" s="3" t="s">
+      <c r="AJ26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E27" s="3">
         <v>8700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>9000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>9800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>9700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>9000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>11100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>11500</v>
-      </c>
-      <c r="N27" s="3">
-        <v>10200</v>
       </c>
       <c r="O27" s="3">
         <v>10200</v>
       </c>
       <c r="P27" s="3">
+        <v>10200</v>
+      </c>
+      <c r="Q27" s="3">
         <v>11200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>9600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>9000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>9700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>8400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>6100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1900</v>
       </c>
-      <c r="AI27" s="3" t="s">
+      <c r="AJ27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2726,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2794,17 +2854,17 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>3</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>3</v>
+      <c r="AA29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>3</v>
@@ -2812,12 +2872,12 @@
       <c r="AD29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>3</v>
       </c>
@@ -2827,8 +2887,11 @@
       <c r="AI29" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2928,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3029,19 +3095,22 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
         <v>0</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
@@ -3049,190 +3118,196 @@
       <c r="H32" s="3">
         <v>0</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>21100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>20900</v>
-      </c>
-      <c r="M32" s="3">
-        <v>18800</v>
       </c>
       <c r="N32" s="3">
         <v>18800</v>
       </c>
       <c r="O32" s="3">
+        <v>18800</v>
+      </c>
+      <c r="P32" s="3">
         <v>17900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>16000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>13700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>11800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>12700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>10500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>12100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>13600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>9300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>11100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>10300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>10200</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>9600</v>
       </c>
       <c r="AB32" s="3">
         <v>9600</v>
       </c>
       <c r="AC32" s="3">
+        <v>9600</v>
+      </c>
+      <c r="AD32" s="3">
         <v>18700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>9600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>10400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>7300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>7000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>7500</v>
       </c>
-      <c r="AI32" s="3" t="s">
+      <c r="AJ32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E33" s="3">
         <v>8700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>9000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>9800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>9700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>9000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>11100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>11500</v>
-      </c>
-      <c r="N33" s="3">
-        <v>10200</v>
       </c>
       <c r="O33" s="3">
         <v>10200</v>
       </c>
       <c r="P33" s="3">
+        <v>10200</v>
+      </c>
+      <c r="Q33" s="3">
         <v>11200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>9600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>9000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>9700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>8400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>6100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1900</v>
       </c>
-      <c r="AI33" s="3" t="s">
+      <c r="AJ33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3332,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E35" s="3">
         <v>8700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>9000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>9800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>9700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>9000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>11100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>11500</v>
-      </c>
-      <c r="N35" s="3">
-        <v>10200</v>
       </c>
       <c r="O35" s="3">
         <v>10200</v>
       </c>
       <c r="P35" s="3">
+        <v>10200</v>
+      </c>
+      <c r="Q35" s="3">
         <v>11200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>9600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>9000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>9700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>8400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>6100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1900</v>
       </c>
-      <c r="AI35" s="3" t="s">
+      <c r="AJ35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2" t="s">
+      <c r="AJ38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3576,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3613,95 +3698,96 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>205300</v>
+      </c>
+      <c r="E41" s="3">
         <v>156700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>136500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>85200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>54000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>146200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>119300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>140400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>20000</v>
-      </c>
-      <c r="L41" s="3">
-        <v>14800</v>
       </c>
       <c r="M41" s="3">
         <v>14800</v>
       </c>
       <c r="N41" s="3">
+        <v>14800</v>
+      </c>
+      <c r="O41" s="3">
         <v>15000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>42900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>23700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>19700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>22700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>18500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>20100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>15600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>11100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>12300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>11600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>10400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>11000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>9800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>9600</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3714,8 +3800,11 @@
       <c r="AI41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3741,68 +3830,68 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>60500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>22500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>236400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>299100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>140700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>300600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>289200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>295600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>128500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>185400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>184100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>165300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>104300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>44000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>67300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>26700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>24300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>29700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>58900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>35500</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3815,23 +3904,26 @@
       <c r="AI42" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ42" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3">
         <v>600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11600</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3841,8 +3933,8 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -3916,8 +4008,11 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3942,8 +4037,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4017,35 +4112,38 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E45" s="3">
         <v>12500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10000</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -4118,35 +4216,38 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>243300</v>
+      </c>
+      <c r="E46" s="3">
         <v>189300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>169200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>119400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>72900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>162200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>139600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>160000</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4219,35 +4320,38 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>223600</v>
+      </c>
+      <c r="E47" s="3">
         <v>208700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>207900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>202300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>208300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>206100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>208500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>255800</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -4320,85 +4424,88 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E48" s="3">
         <v>6000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>12200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3000</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>2800</v>
       </c>
       <c r="AC48" s="3">
         <v>2800</v>
@@ -4406,8 +4513,8 @@
       <c r="AD48" s="3">
         <v>2800</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>3</v>
+      <c r="AE48" s="3">
+        <v>2800</v>
       </c>
       <c r="AF48" s="3" t="s">
         <v>3</v>
@@ -4421,13 +4528,16 @@
       <c r="AI48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>42500</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
@@ -4522,8 +4632,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4623,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4724,82 +4840,85 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>83900</v>
+      </c>
+      <c r="E52" s="3">
         <v>70500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>53000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>50600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>52900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>50900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>50000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>49300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>13800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7200</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>7400</v>
       </c>
       <c r="R52" s="3">
         <v>7400</v>
       </c>
       <c r="S52" s="3">
+        <v>7400</v>
+      </c>
+      <c r="T52" s="3">
         <v>6800</v>
-      </c>
-      <c r="T52" s="3">
-        <v>3600</v>
       </c>
       <c r="U52" s="3">
         <v>3600</v>
       </c>
       <c r="V52" s="3">
+        <v>3600</v>
+      </c>
+      <c r="W52" s="3">
         <v>4000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3600</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>3700</v>
       </c>
       <c r="AB52" s="3">
         <v>3700</v>
@@ -4808,11 +4927,11 @@
         <v>3700</v>
       </c>
       <c r="AD52" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AE52" s="3">
         <v>3600</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4825,8 +4944,11 @@
       <c r="AI52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4926,95 +5048,98 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3206900</v>
+      </c>
+      <c r="E54" s="3">
         <v>2560800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2438600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2324200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2226200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2272500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2227900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2245300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2123700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2009400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2154800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2122500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2055300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2169600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2151900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2091900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1876600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1879000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1822400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1507800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1427600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1311400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1234200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1123800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1105100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1072900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1067800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1017600</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5027,8 +5152,11 @@
       <c r="AI54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5064,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5101,95 +5230,96 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2761900</v>
+      </c>
+      <c r="E57" s="3">
         <v>2186200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2100400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2005700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1896000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1968000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1934400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1944400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>300</v>
-      </c>
-      <c r="N57" s="3">
-        <v>500</v>
       </c>
       <c r="O57" s="3">
         <v>500</v>
       </c>
       <c r="P57" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q57" s="3">
         <v>800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2100</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>2000</v>
       </c>
       <c r="Z57" s="3">
         <v>2000</v>
       </c>
       <c r="AA57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AB57" s="3">
         <v>1600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1400</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5202,35 +5332,38 @@
       <c r="AI57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E58" s="3">
         <v>200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>800</v>
       </c>
-      <c r="G58" s="3">
-        <v>16200</v>
-      </c>
       <c r="H58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="I58" s="3">
         <v>300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10900</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -5303,8 +5436,11 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5329,57 +5465,57 @@
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3">
         <v>2400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5100</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5389,8 +5525,8 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE59" s="3">
-        <v>0</v>
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF59" s="3">
         <v>0</v>
@@ -5404,35 +5540,38 @@
       <c r="AI59" s="3">
         <v>0</v>
       </c>
+      <c r="AJ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2795400</v>
+      </c>
+      <c r="E60" s="3">
         <v>2195000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2107600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2012500</v>
       </c>
-      <c r="G60" s="3">
-        <v>1917700</v>
-      </c>
       <c r="H60" s="3">
+        <v>1916600</v>
+      </c>
+      <c r="I60" s="3">
         <v>1973500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1938100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1957300</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5505,34 +5644,37 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E61" s="3">
         <v>68200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>47900</v>
-      </c>
-      <c r="F61" s="3">
-        <v>36700</v>
       </c>
       <c r="G61" s="3">
         <v>36700</v>
       </c>
       <c r="H61" s="3">
-        <v>37700</v>
+        <v>37900</v>
       </c>
       <c r="I61" s="3">
         <v>37700</v>
       </c>
       <c r="J61" s="3">
+        <v>37700</v>
+      </c>
+      <c r="K61" s="3">
         <v>37200</v>
-      </c>
-      <c r="K61" s="3">
-        <v>12100</v>
       </c>
       <c r="L61" s="3">
         <v>12100</v>
@@ -5556,16 +5698,16 @@
         <v>12100</v>
       </c>
       <c r="S61" s="3">
+        <v>12100</v>
+      </c>
+      <c r="T61" s="3">
         <v>14000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>17500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>17400</v>
-      </c>
-      <c r="V61" s="3">
-        <v>15400</v>
       </c>
       <c r="W61" s="3">
         <v>15400</v>
@@ -5586,14 +5728,14 @@
         <v>15400</v>
       </c>
       <c r="AC61" s="3">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>15400</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
@@ -5606,35 +5748,38 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>40500</v>
+      </c>
+      <c r="E62" s="3">
         <v>17500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>15200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>15500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>16900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>18400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>14700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>16300</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -5707,8 +5852,11 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5808,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5909,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6010,95 +6164,98 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2851800</v>
+      </c>
+      <c r="E66" s="3">
         <v>2280700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2170700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2064800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1971300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2029600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1990400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2010800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1899600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1795400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1947500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1921000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1857400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1980500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1974600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1924800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1717300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1729700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1680300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1371800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1294300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1183600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1111000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1005200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>990500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>966200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>980800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>934200</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6111,8 +6268,11 @@
       <c r="AI66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6148,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6249,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6350,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6451,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6552,95 +6722,98 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>237800</v>
+      </c>
+      <c r="E72" s="3">
         <v>233000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>225800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>218700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>213300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>206000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>197500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>191100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>182400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>174900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>164800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>153900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>144500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>135900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>125400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>115800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>106900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>97600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>89200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>84400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>81600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>77100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>72900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>68900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>65700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>62500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>59300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>56200</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6653,8 +6826,11 @@
       <c r="AI72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6754,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6855,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6956,95 +7138,98 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>355100</v>
+      </c>
+      <c r="E76" s="3">
         <v>280100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>267900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>259500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>254900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>242900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>237400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>234500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>224000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>214000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>207300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>201500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>197900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>189100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>177200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>167000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>159300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>149400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>142100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>136100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>133300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>127800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>123100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>118600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>114600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>106700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>87000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>83400</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7057,8 +7242,11 @@
       <c r="AI76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7158,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2" t="s">
+      <c r="AJ80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E81" s="3">
         <v>8700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>9000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>9800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>9700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>9000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>11100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>11500</v>
-      </c>
-      <c r="N81" s="3">
-        <v>10200</v>
       </c>
       <c r="O81" s="3">
         <v>10200</v>
       </c>
       <c r="P81" s="3">
+        <v>10200</v>
+      </c>
+      <c r="Q81" s="3">
         <v>11200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>9600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>9000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>9700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>8400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>6100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1900</v>
       </c>
-      <c r="AI81" s="3" t="s">
+      <c r="AJ81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7402,19 +7599,20 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E83" s="3">
         <v>400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-100</v>
-      </c>
-      <c r="F83" s="3">
-        <v>300</v>
       </c>
       <c r="G83" s="3">
         <v>300</v>
@@ -7423,49 +7621,49 @@
         <v>300</v>
       </c>
       <c r="I83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J83" s="3">
         <v>400</v>
       </c>
       <c r="K83" s="3">
+        <v>400</v>
+      </c>
+      <c r="L83" s="3">
         <v>-700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>300</v>
-      </c>
-      <c r="M83" s="3">
-        <v>400</v>
       </c>
       <c r="N83" s="3">
         <v>400</v>
       </c>
       <c r="O83" s="3">
+        <v>400</v>
+      </c>
+      <c r="P83" s="3">
         <v>-500</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="R83" s="3">
         <v>500</v>
       </c>
       <c r="S83" s="3">
+        <v>500</v>
+      </c>
+      <c r="T83" s="3">
         <v>-600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>500</v>
-      </c>
-      <c r="W83" s="3">
-        <v>300</v>
       </c>
       <c r="X83" s="3">
         <v>300</v>
@@ -7480,31 +7678,34 @@
         <v>300</v>
       </c>
       <c r="AB83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC83" s="3">
         <v>200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>300</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF83" s="3">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG83" s="3">
         <v>200</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7604,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7705,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7806,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7907,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8008,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>12900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>22500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>15800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>20300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>29500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>26400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>21500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>54600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>41300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-8900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-30100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>8200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-14800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-21500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>10400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>15100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>12900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>6800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>4700</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8146,71 +8365,72 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E91" s="3">
         <v>600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3">
         <v>400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-2300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-200</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-700</v>
       </c>
       <c r="M91" s="3">
         <v>-700</v>
       </c>
       <c r="N91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S91" s="3">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="3">
         <v>100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
@@ -8220,35 +8440,38 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-700</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>-400</v>
       </c>
       <c r="AE91" s="3">
         <v>-400</v>
       </c>
       <c r="AF91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-300</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8348,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8449,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-63100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-83700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-65500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-57600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-39100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-26300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-58700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-68000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-77700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-108800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>56100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-45900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-85300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-92600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-86000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-34000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-249500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-16000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-57300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-81700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-42500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-6400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-43400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-33800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-32000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-12000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-16700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-32300</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8587,16 +8819,17 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E96" s="3">
         <v>1400</v>
-      </c>
-      <c r="E96" s="3">
-        <v>1100</v>
       </c>
       <c r="F96" s="3">
         <v>1100</v>
@@ -8608,25 +8841,25 @@
         <v>1100</v>
       </c>
       <c r="I96" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J96" s="3">
         <v>800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>900</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-800</v>
       </c>
       <c r="L96" s="3">
         <v>-800</v>
       </c>
       <c r="M96" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="N96" s="3">
         <v>-700</v>
       </c>
       <c r="O96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -8688,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8789,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8890,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8991,109 +9233,115 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>85800</v>
+      </c>
+      <c r="E100" s="3">
         <v>104400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>103900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>92300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-59200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>30600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-22700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>108300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>105300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-151900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>25600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>65100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-124300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>54400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>209100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-14000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>48700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>304400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>73000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>109700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>72100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>105200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>8300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>27000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>3000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>33300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-10600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>22700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>16600</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9118,8 +9366,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9193,105 +9441,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>48600</v>
+      </c>
+      <c r="E102" s="3">
         <v>20200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>51300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>31200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-92200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>26800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-21000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>60000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>43400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-213800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-62900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>130400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-140600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>15300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-9400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>171100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-58600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>5800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>24800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>60000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>59700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-24500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>41200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>3600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-28000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>16400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-9700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>12700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-10900</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CBNK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CBNK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="92">
   <si>
     <t>CBNK</t>
   </si>
@@ -656,259 +656,266 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2" t="s">
+      <c r="AK7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>56400</v>
+      </c>
+      <c r="E8" s="3">
         <v>50900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>41200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>40400</v>
-      </c>
-      <c r="G8" s="3">
-        <v>38100</v>
       </c>
       <c r="H8" s="3">
         <v>38100</v>
       </c>
       <c r="I8" s="3">
+        <v>38100</v>
+      </c>
+      <c r="J8" s="3">
         <v>40800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>39200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>38900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>41300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>38300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>36600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>34400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>33800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>33500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>29300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>26600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>28300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>25200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>22000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>21700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>21200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>22400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>20300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>18300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>18200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>17400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>33400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>16700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>14700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>15000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>14200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>12800</v>
       </c>
-      <c r="AJ8" s="3" t="s">
+      <c r="AK8" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1011,38 +1018,41 @@
       <c r="AJ9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>56400</v>
+      </c>
+      <c r="E10" s="3">
         <v>50900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>41200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>40400</v>
-      </c>
-      <c r="G10" s="3">
-        <v>38100</v>
       </c>
       <c r="H10" s="3">
         <v>38100</v>
       </c>
       <c r="I10" s="3">
+        <v>38100</v>
+      </c>
+      <c r="J10" s="3">
         <v>40800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>39200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>38900</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1115,8 +1125,11 @@
       <c r="AJ10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,8 +1166,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1257,8 +1271,11 @@
       <c r="AJ12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,26 +1378,29 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E14" s="3">
         <v>5200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>700</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1390,8 +1410,8 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1465,16 +1485,19 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>500</v>
+      </c>
+      <c r="E15" s="3">
         <v>800</v>
-      </c>
-      <c r="E15" s="3">
-        <v>100</v>
       </c>
       <c r="F15" s="3">
         <v>100</v>
@@ -1495,7 +1518,7 @@
         <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1569,8 +1592,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1630,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>36800</v>
+      </c>
+      <c r="E17" s="3">
         <v>34900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>29200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>29400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>28800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>26900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>28000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>29600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>26200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ17" s="3" t="s">
+      <c r="AK17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E18" s="3">
         <v>16000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>12000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>11000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>9300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>11200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>12800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>12700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>32800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>35400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>33400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>32400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>31600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>31100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>26800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>23900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>25700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>22100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>18600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>17600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>15900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>17200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>15900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>14600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>14400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>14000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>27300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>13900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>11800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>12300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>11700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>10500</v>
       </c>
-      <c r="AJ18" s="3" t="s">
+      <c r="AK18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,8 +1883,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1861,11 +1895,11 @@
       <c r="E20" s="3">
         <v>0</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -1873,193 +1907,199 @@
       <c r="I20" s="3">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-21100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-20900</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-18800</v>
       </c>
       <c r="O20" s="3">
         <v>-18800</v>
       </c>
       <c r="P20" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-17900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-16000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-13700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-11800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-12700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-10500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-12100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-13600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-11100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-10300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-10200</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>-9600</v>
       </c>
       <c r="AC20" s="3">
         <v>-9600</v>
       </c>
       <c r="AD20" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-18700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-9600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-10400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-7300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-7000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-7500</v>
       </c>
-      <c r="AJ20" s="3" t="s">
+      <c r="AK20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E21" s="3">
         <v>16800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>12100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>11100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>11300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>12900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>12700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>10900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>14800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>15000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>14000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>13200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>15100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>13500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>12600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>12500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>12100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>6900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>6400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>5900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>5100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>9200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>5200</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ21" s="3" t="s">
+      <c r="AK21" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2087,8 +2127,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2162,216 +2202,225 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E23" s="3">
         <v>10800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>11500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>10900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>8600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>11200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>12800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>12700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>11600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>14400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>14600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>13600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>13700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>15100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>13000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>12100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>13000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>11600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>6100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>5600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>8700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>5000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>4700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ23" s="3" t="s">
+      <c r="AK23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E24" s="3">
         <v>3200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1100</v>
-      </c>
-      <c r="X24" s="3">
-        <v>1600</v>
       </c>
       <c r="Y24" s="3">
         <v>1600</v>
       </c>
       <c r="Z24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AA24" s="3">
         <v>1500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ24" s="3" t="s">
+      <c r="AK24" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2523,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E26" s="3">
         <v>7500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>9000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>9800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>9700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>11100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>11500</v>
-      </c>
-      <c r="O26" s="3">
-        <v>10200</v>
       </c>
       <c r="P26" s="3">
         <v>10200</v>
       </c>
       <c r="Q26" s="3">
+        <v>10200</v>
+      </c>
+      <c r="R26" s="3">
         <v>11200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>9600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>9000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>9700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>8400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>6100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ26" s="3" t="s">
+      <c r="AK26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E27" s="3">
         <v>7500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>9000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>9800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>9700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>9000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>11100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>11500</v>
-      </c>
-      <c r="O27" s="3">
-        <v>10200</v>
       </c>
       <c r="P27" s="3">
         <v>10200</v>
       </c>
       <c r="Q27" s="3">
+        <v>10200</v>
+      </c>
+      <c r="R27" s="3">
         <v>11200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>9600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>9000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>9700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>8400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>6100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ27" s="3" t="s">
+      <c r="AK27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2844,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2857,17 +2918,17 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>3</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>3</v>
+      <c r="AB29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>3</v>
@@ -2875,12 +2936,12 @@
       <c r="AE29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>3</v>
       </c>
@@ -2890,8 +2951,11 @@
       <c r="AJ29" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3058,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,8 +3165,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3109,11 +3179,11 @@
       <c r="E32" s="3">
         <v>0</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
@@ -3121,193 +3191,199 @@
       <c r="I32" s="3">
         <v>0</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>21100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>20900</v>
-      </c>
-      <c r="N32" s="3">
-        <v>18800</v>
       </c>
       <c r="O32" s="3">
         <v>18800</v>
       </c>
       <c r="P32" s="3">
+        <v>18800</v>
+      </c>
+      <c r="Q32" s="3">
         <v>17900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>16000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>13700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>11800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>12700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>10500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>12100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>13600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>9300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>11100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>10300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>10200</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>9600</v>
       </c>
       <c r="AC32" s="3">
         <v>9600</v>
       </c>
       <c r="AD32" s="3">
+        <v>9600</v>
+      </c>
+      <c r="AE32" s="3">
         <v>18700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>9600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>10400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>7300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>7000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>7500</v>
       </c>
-      <c r="AJ32" s="3" t="s">
+      <c r="AK32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E33" s="3">
         <v>7500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>9000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>9800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>9700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>9000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>11100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>11500</v>
-      </c>
-      <c r="O33" s="3">
-        <v>10200</v>
       </c>
       <c r="P33" s="3">
         <v>10200</v>
       </c>
       <c r="Q33" s="3">
+        <v>10200</v>
+      </c>
+      <c r="R33" s="3">
         <v>11200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>9600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>9000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>9700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>8400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>6100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ33" s="3" t="s">
+      <c r="AK33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3486,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E35" s="3">
         <v>7500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>9000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>9800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>9700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>9000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>11100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>11500</v>
-      </c>
-      <c r="O35" s="3">
-        <v>10200</v>
       </c>
       <c r="P35" s="3">
         <v>10200</v>
       </c>
       <c r="Q35" s="3">
+        <v>10200</v>
+      </c>
+      <c r="R35" s="3">
         <v>11200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>9600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>9000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>9700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>8400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>6100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ35" s="3" t="s">
+      <c r="AK35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2" t="s">
+      <c r="AK38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3746,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,98 +3785,99 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>294000</v>
+      </c>
+      <c r="E41" s="3">
         <v>205300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>156700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>136500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>85200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>54000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>146200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>119300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>140400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>20000</v>
-      </c>
-      <c r="M41" s="3">
-        <v>14800</v>
       </c>
       <c r="N41" s="3">
         <v>14800</v>
       </c>
       <c r="O41" s="3">
+        <v>14800</v>
+      </c>
+      <c r="P41" s="3">
         <v>15000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>42900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>23700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>19700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>22700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>18500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>20100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>15600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>11100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>12300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>11600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>10400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>11000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>9800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>9600</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3803,8 +3890,11 @@
       <c r="AJ41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3833,68 +3923,68 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>60500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>22500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>236400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>299100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>140700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>300600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>289200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>295600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>128500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>185400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>184100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>165300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>104300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>44000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>67300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>26700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>24300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>29700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>58900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>35500</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3907,26 +3997,29 @@
       <c r="AJ42" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK42" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3">
         <v>600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11600</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3936,8 +4029,8 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -4011,8 +4104,11 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4040,8 +4136,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4115,38 +4211,41 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E45" s="3">
         <v>16700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10000</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -4219,38 +4318,41 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>348100</v>
+      </c>
+      <c r="E46" s="3">
         <v>243300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>189300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>169200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>119400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>72900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>162200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>139600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>160000</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4323,38 +4425,41 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>213500</v>
+      </c>
+      <c r="E47" s="3">
         <v>223600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>208700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>207900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>202300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>208300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>206100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>208500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>255800</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -4427,88 +4532,91 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E48" s="3">
         <v>15500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>12200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3000</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>2800</v>
       </c>
       <c r="AD48" s="3">
         <v>2800</v>
@@ -4516,8 +4624,8 @@
       <c r="AE48" s="3">
         <v>2800</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>3</v>
+      <c r="AF48" s="3">
+        <v>2800</v>
       </c>
       <c r="AG48" s="3" t="s">
         <v>3</v>
@@ -4531,17 +4639,20 @@
       <c r="AJ48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E49" s="3">
         <v>42500</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
       <c r="F49" s="3">
         <v>0</v>
       </c>
@@ -4635,8 +4746,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4853,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,85 +4960,88 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>85400</v>
+      </c>
+      <c r="E52" s="3">
         <v>83900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>70500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>53000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>50600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>52900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>50900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>50000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>49300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>13800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>12400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>9800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7200</v>
-      </c>
-      <c r="R52" s="3">
-        <v>7400</v>
       </c>
       <c r="S52" s="3">
         <v>7400</v>
       </c>
       <c r="T52" s="3">
+        <v>7400</v>
+      </c>
+      <c r="U52" s="3">
         <v>6800</v>
-      </c>
-      <c r="U52" s="3">
-        <v>3600</v>
       </c>
       <c r="V52" s="3">
         <v>3600</v>
       </c>
       <c r="W52" s="3">
+        <v>3600</v>
+      </c>
+      <c r="X52" s="3">
         <v>4000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3600</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>3700</v>
       </c>
       <c r="AC52" s="3">
         <v>3700</v>
@@ -4930,11 +5050,11 @@
         <v>3700</v>
       </c>
       <c r="AE52" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AF52" s="3">
         <v>3600</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4947,8 +5067,11 @@
       <c r="AJ52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,98 +5174,101 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3349800</v>
+      </c>
+      <c r="E54" s="3">
         <v>3206900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2560800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2438600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2324200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2226200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2272500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2227900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2245300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2123700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2009400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2154800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2122500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2055300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2169600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2151900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2091900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1876600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1879000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1822400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1507800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1427600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1311400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1234200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1123800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1105100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1072900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1067800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1017600</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5155,8 +5281,11 @@
       <c r="AJ54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5322,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,98 +5361,99 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2891300</v>
+      </c>
+      <c r="E57" s="3">
         <v>2761900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2186200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2100400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2005700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1896000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1968000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1934400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1944400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>300</v>
-      </c>
-      <c r="O57" s="3">
-        <v>500</v>
       </c>
       <c r="P57" s="3">
         <v>500</v>
       </c>
       <c r="Q57" s="3">
+        <v>500</v>
+      </c>
+      <c r="R57" s="3">
         <v>800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2100</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>2000</v>
       </c>
       <c r="AA57" s="3">
         <v>2000</v>
       </c>
       <c r="AB57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AC57" s="3">
         <v>1600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1400</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5335,38 +5466,41 @@
       <c r="AJ57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E58" s="3">
         <v>24000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>15000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10900</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -5439,8 +5573,11 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5468,57 +5605,57 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>2400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5100</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5528,8 +5665,8 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF59" s="3">
-        <v>0</v>
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG59" s="3">
         <v>0</v>
@@ -5543,38 +5680,41 @@
       <c r="AJ59" s="3">
         <v>0</v>
       </c>
+      <c r="AK59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2924900</v>
+      </c>
+      <c r="E60" s="3">
         <v>2795400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2195000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2107600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2012500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1916600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1973500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1938100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1957300</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5647,37 +5787,40 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E61" s="3">
         <v>15900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>68200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>47900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>36700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>37900</v>
-      </c>
-      <c r="I61" s="3">
-        <v>37700</v>
       </c>
       <c r="J61" s="3">
         <v>37700</v>
       </c>
       <c r="K61" s="3">
+        <v>37700</v>
+      </c>
+      <c r="L61" s="3">
         <v>37200</v>
-      </c>
-      <c r="L61" s="3">
-        <v>12100</v>
       </c>
       <c r="M61" s="3">
         <v>12100</v>
@@ -5701,16 +5844,16 @@
         <v>12100</v>
       </c>
       <c r="T61" s="3">
+        <v>12100</v>
+      </c>
+      <c r="U61" s="3">
         <v>14000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>17500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>17400</v>
-      </c>
-      <c r="W61" s="3">
-        <v>15400</v>
       </c>
       <c r="X61" s="3">
         <v>15400</v>
@@ -5731,14 +5874,14 @@
         <v>15400</v>
       </c>
       <c r="AD61" s="3">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>15400</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
@@ -5751,38 +5894,41 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E62" s="3">
         <v>40500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>17500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>15200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>15500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>16900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>18400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16300</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -5855,8 +6001,11 @@
       <c r="AJ62" s="3">
         <v>0</v>
       </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6108,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6215,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,98 +6322,101 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2980200</v>
+      </c>
+      <c r="E66" s="3">
         <v>2851800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2280700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2170700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2064800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1971300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2029600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1990400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2010800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1899600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1795400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1947500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1921000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1857400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1980500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1974600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1924800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1717300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1729700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1680300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1371800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1294300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1183600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1111000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1005200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>990500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>966200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>980800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>934200</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6271,8 +6429,11 @@
       <c r="AJ66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6470,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6575,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6682,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6789,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,98 +6896,101 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>249900</v>
+      </c>
+      <c r="E72" s="3">
         <v>237800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>233000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>225800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>218700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>213300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>206000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>197500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>191100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>182400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>174900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>164800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>153900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>144500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>135900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>125400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>115800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>106900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>97600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>89200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>84400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>81600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>77100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>72900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>68900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>65700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>62500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>59300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>56200</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6829,8 +7003,11 @@
       <c r="AJ72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7110,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7217,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,98 +7324,101 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>369600</v>
+      </c>
+      <c r="E76" s="3">
         <v>355100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>280100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>267900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>259500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>254900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>242900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>237400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>234500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>224000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>214000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>207300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>201500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>197900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>189100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>177200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>167000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>159300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>149400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>142100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>136100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>133300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>127800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>123100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>118600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>114600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>106700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>87000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>83400</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7245,8 +7431,11 @@
       <c r="AJ76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7538,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2" t="s">
+      <c r="AK80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E81" s="3">
         <v>7500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>9000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>9800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>9700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>9000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>11100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>11500</v>
-      </c>
-      <c r="O81" s="3">
-        <v>10200</v>
       </c>
       <c r="P81" s="3">
         <v>10200</v>
       </c>
       <c r="Q81" s="3">
+        <v>10200</v>
+      </c>
+      <c r="R81" s="3">
         <v>11200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>9600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>9000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>9700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>8400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>6100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ81" s="3" t="s">
+      <c r="AK81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,22 +7798,23 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>300</v>
+      </c>
+      <c r="E83" s="3">
         <v>-200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>-100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>300</v>
       </c>
       <c r="H83" s="3">
         <v>300</v>
@@ -7624,49 +7823,49 @@
         <v>300</v>
       </c>
       <c r="J83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K83" s="3">
         <v>400</v>
       </c>
       <c r="L83" s="3">
+        <v>400</v>
+      </c>
+      <c r="M83" s="3">
         <v>-700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>300</v>
-      </c>
-      <c r="N83" s="3">
-        <v>400</v>
       </c>
       <c r="O83" s="3">
         <v>400</v>
       </c>
       <c r="P83" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q83" s="3">
         <v>-500</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
       <c r="R83" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="S83" s="3">
         <v>500</v>
       </c>
       <c r="T83" s="3">
+        <v>500</v>
+      </c>
+      <c r="U83" s="3">
         <v>-600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>500</v>
-      </c>
-      <c r="X83" s="3">
-        <v>300</v>
       </c>
       <c r="Y83" s="3">
         <v>300</v>
@@ -7681,31 +7880,34 @@
         <v>300</v>
       </c>
       <c r="AC83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD83" s="3">
         <v>200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>300</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG83" s="3">
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH83" s="3">
         <v>200</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8010,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8117,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8224,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8331,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8438,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E89" s="3">
         <v>25900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>12900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>22500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>8400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>10400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>15800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>20300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>29500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>26400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>21500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>54600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>41300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-8900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-30100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>8200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-14800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-21500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>10400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>15100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>12900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>6800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>4700</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,74 +8586,75 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3">
         <v>400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-2300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-700</v>
       </c>
       <c r="N91" s="3">
         <v>-700</v>
       </c>
       <c r="O91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T91" s="3">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U91" s="3">
         <v>100</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
@@ -8443,35 +8664,38 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-700</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>-400</v>
       </c>
       <c r="AF91" s="3">
         <v>-400</v>
       </c>
       <c r="AG91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-300</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8798,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8905,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-61100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-63100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-83700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-65500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-57600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-39100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-26300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-58700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-68000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-77700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-108800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>56100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-45900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-14500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-85300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-92600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-86000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-34000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-249500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-16000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-57300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-81700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-42500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-6400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-43400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-33800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-32000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-12000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-16700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-32300</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9053,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8829,10 +9063,10 @@
         <v>1700</v>
       </c>
       <c r="E96" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F96" s="3">
         <v>1400</v>
-      </c>
-      <c r="F96" s="3">
-        <v>1100</v>
       </c>
       <c r="G96" s="3">
         <v>1100</v>
@@ -8844,25 +9078,25 @@
         <v>1100</v>
       </c>
       <c r="J96" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K96" s="3">
         <v>800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>900</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-800</v>
       </c>
       <c r="M96" s="3">
         <v>-800</v>
       </c>
       <c r="N96" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="O96" s="3">
         <v>-700</v>
       </c>
       <c r="P96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -8924,8 +9158,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9265,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9372,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,112 +9479,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>127200</v>
+      </c>
+      <c r="E100" s="3">
         <v>85800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>104400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>103900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>92300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-59200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>30600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-22700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>108300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>105300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-151900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>25600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>65100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-124300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>54400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>209100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-14000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>48700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>304400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>73000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>109700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>72100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>105200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>8300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>27000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>3000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>33300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-10600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>22700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>16600</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9369,8 +9618,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9444,108 +9693,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>88700</v>
+      </c>
+      <c r="E102" s="3">
         <v>48600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>20200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>51300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>31200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-92200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>26800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-21000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>60000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>43400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-213800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-62900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>130400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-140600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>15300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-9400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>171100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-58600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>5800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>24800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>60000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>59700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-24500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>41200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-28000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>16400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-9700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>12700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-10900</v>
       </c>
-      <c r="AH102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CBNK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CBNK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="92">
   <si>
     <t>CBNK</t>
   </si>
@@ -656,266 +656,273 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2" t="s">
+      <c r="AL7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>56700</v>
+      </c>
+      <c r="E8" s="3">
         <v>56400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>50900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>41200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>40400</v>
-      </c>
-      <c r="H8" s="3">
-        <v>38100</v>
       </c>
       <c r="I8" s="3">
         <v>38100</v>
       </c>
       <c r="J8" s="3">
+        <v>38100</v>
+      </c>
+      <c r="K8" s="3">
         <v>40800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>39200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>38900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>41300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>38300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>36600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>34400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>33800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>33500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>29300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>26600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>28300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>25200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>22000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>21700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>21200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>22400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>20300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>18300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>18200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>17400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>33400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>16700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>14700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>15000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>14200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>12800</v>
       </c>
-      <c r="AK8" s="3" t="s">
+      <c r="AL8" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1021,41 +1028,44 @@
       <c r="AK9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>56700</v>
+      </c>
+      <c r="E10" s="3">
         <v>56400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>50900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>41200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>40400</v>
-      </c>
-      <c r="H10" s="3">
-        <v>38100</v>
       </c>
       <c r="I10" s="3">
         <v>38100</v>
       </c>
       <c r="J10" s="3">
+        <v>38100</v>
+      </c>
+      <c r="K10" s="3">
         <v>40800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>39200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>38900</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1128,8 +1138,11 @@
       <c r="AK10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1167,8 +1180,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1274,8 +1288,11 @@
       <c r="AK12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1381,29 +1398,32 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E14" s="3">
         <v>1300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>5200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>700</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1413,8 +1433,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1488,19 +1508,22 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>600</v>
+      </c>
+      <c r="E15" s="3">
         <v>500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>800</v>
-      </c>
-      <c r="F15" s="3">
-        <v>100</v>
       </c>
       <c r="G15" s="3">
         <v>100</v>
@@ -1521,7 +1544,7 @@
         <v>100</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1595,8 +1618,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,222 +1657,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E17" s="3">
         <v>36800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>34900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>29200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>29400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>28800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>26900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>28000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>29600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>26200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2300</v>
       </c>
-      <c r="AK17" s="3" t="s">
+      <c r="AL17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E18" s="3">
         <v>19600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>16000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>12000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>11000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>9300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>11200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>12800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>12700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>32800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>35400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>33400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>32400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>31600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>31100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>26800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>23900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>25700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>22100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>18600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>17600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>15900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>17200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>15900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>14600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>14400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>14000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>27300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>13900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>11800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>12300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>11700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>10500</v>
       </c>
-      <c r="AK18" s="3" t="s">
+      <c r="AL18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1884,13 +1917,14 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1898,11 +1932,11 @@
       <c r="F20" s="3">
         <v>0</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
@@ -1910,196 +1944,202 @@
       <c r="J20" s="3">
         <v>0</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-21100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-20900</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-18800</v>
       </c>
       <c r="P20" s="3">
         <v>-18800</v>
       </c>
       <c r="Q20" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="R20" s="3">
         <v>-17900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-16000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-13700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-11800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-12700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-10500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-12100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-13600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-9300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-11100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-10300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-10200</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>-9600</v>
       </c>
       <c r="AD20" s="3">
         <v>-9600</v>
       </c>
       <c r="AE20" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-18700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-9600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-10400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-7300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-7000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-7500</v>
       </c>
-      <c r="AK20" s="3" t="s">
+      <c r="AL20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E21" s="3">
         <v>20000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>16800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>12100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>11100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>9400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>11300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>12900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>12700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>10900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>14800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>15000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>14000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>13200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>15100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>13500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>12600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>12500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>12100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>6900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>6900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>6400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>5900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>5100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>9200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>5200</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ21" s="3">
+      <c r="AJ21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK21" s="3">
         <v>3300</v>
       </c>
-      <c r="AK21" s="3" t="s">
+      <c r="AL21" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2130,8 +2170,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2205,222 +2245,231 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E23" s="3">
         <v>18300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>10800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>11500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>10900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>11200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>12800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>12700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>11600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>14400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>14600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>13600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>13700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>15100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>13000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>12100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>13000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>11600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>6700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>6100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>5600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>8700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>5000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>3000</v>
       </c>
-      <c r="AK23" s="3" t="s">
+      <c r="AL23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E24" s="3">
         <v>4400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1100</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>1600</v>
       </c>
       <c r="Z24" s="3">
         <v>1600</v>
       </c>
       <c r="AA24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AB24" s="3">
         <v>1500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1200</v>
       </c>
-      <c r="AK24" s="3" t="s">
+      <c r="AL24" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2526,222 +2575,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E26" s="3">
         <v>13900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>8200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>9000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>9800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>9000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>11100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>11500</v>
-      </c>
-      <c r="P26" s="3">
-        <v>10200</v>
       </c>
       <c r="Q26" s="3">
         <v>10200</v>
       </c>
       <c r="R26" s="3">
+        <v>10200</v>
+      </c>
+      <c r="S26" s="3">
         <v>11200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>9600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>9000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>9700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>8400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>5100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>6100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1900</v>
       </c>
-      <c r="AK26" s="3" t="s">
+      <c r="AL26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E27" s="3">
         <v>13900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>8200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>9000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>9800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>9700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>9000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>11100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>11500</v>
-      </c>
-      <c r="P27" s="3">
-        <v>10200</v>
       </c>
       <c r="Q27" s="3">
         <v>10200</v>
       </c>
       <c r="R27" s="3">
+        <v>10200</v>
+      </c>
+      <c r="S27" s="3">
         <v>11200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>9600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>9000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>9700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>8400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>5100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>6100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>3000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1900</v>
       </c>
-      <c r="AK27" s="3" t="s">
+      <c r="AL27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2847,8 +2905,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2921,17 +2982,17 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>3</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>3</v>
+      <c r="AC29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>3</v>
@@ -2939,12 +3000,12 @@
       <c r="AF29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>3</v>
       </c>
@@ -2954,8 +3015,11 @@
       <c r="AK29" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3125,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,13 +3235,16 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -3182,11 +3252,11 @@
       <c r="F32" s="3">
         <v>0</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
@@ -3194,196 +3264,202 @@
       <c r="J32" s="3">
         <v>0</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>21100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>20900</v>
-      </c>
-      <c r="O32" s="3">
-        <v>18800</v>
       </c>
       <c r="P32" s="3">
         <v>18800</v>
       </c>
       <c r="Q32" s="3">
+        <v>18800</v>
+      </c>
+      <c r="R32" s="3">
         <v>17900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>16000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>13700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>11800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>12700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>10500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>12100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>13600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>9300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>11100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>10300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>10200</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>9600</v>
       </c>
       <c r="AD32" s="3">
         <v>9600</v>
       </c>
       <c r="AE32" s="3">
+        <v>9600</v>
+      </c>
+      <c r="AF32" s="3">
         <v>18700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>9600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>10400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>7300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>7500</v>
       </c>
-      <c r="AK32" s="3" t="s">
+      <c r="AL32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E33" s="3">
         <v>13900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>8200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>9000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>9800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>9700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>9000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>11100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>11500</v>
-      </c>
-      <c r="P33" s="3">
-        <v>10200</v>
       </c>
       <c r="Q33" s="3">
         <v>10200</v>
       </c>
       <c r="R33" s="3">
+        <v>10200</v>
+      </c>
+      <c r="S33" s="3">
         <v>11200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>9600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>9000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>9700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>8400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>5100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>4000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>6100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>3000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1900</v>
       </c>
-      <c r="AK33" s="3" t="s">
+      <c r="AL33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,227 +3565,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E35" s="3">
         <v>13900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>8200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>9000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>9800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>9700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>9000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>11100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>11500</v>
-      </c>
-      <c r="P35" s="3">
-        <v>10200</v>
       </c>
       <c r="Q35" s="3">
         <v>10200</v>
       </c>
       <c r="R35" s="3">
+        <v>10200</v>
+      </c>
+      <c r="S35" s="3">
         <v>11200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>9600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>9000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>9700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>8400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>5100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>4000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>6100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>3000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1900</v>
       </c>
-      <c r="AK35" s="3" t="s">
+      <c r="AL35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2" t="s">
+      <c r="AL38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +3832,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,101 +3872,102 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>274600</v>
+      </c>
+      <c r="E41" s="3">
         <v>294000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>205300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>156700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>136500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>85200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>54000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>146200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>119300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>140400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>20000</v>
-      </c>
-      <c r="N41" s="3">
-        <v>14800</v>
       </c>
       <c r="O41" s="3">
         <v>14800</v>
       </c>
       <c r="P41" s="3">
+        <v>14800</v>
+      </c>
+      <c r="Q41" s="3">
         <v>15000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>42900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>23700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>19700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>22700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>18500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>20100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>15600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>10500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>11100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>12300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>11600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>10400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>11000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>9800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>9600</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3893,8 +3980,11 @@
       <c r="AK41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3926,68 +4016,68 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>60500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>22500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>236400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>299100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>140700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>300600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>289200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>295600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>128500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>185400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>184100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>165300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>104300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>44000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>67300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>26700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>24300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>29700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>58900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>35500</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH42" s="3" t="s">
         <v>3</v>
       </c>
@@ -4000,8 +4090,11 @@
       <c r="AK42" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL42" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4011,18 +4104,18 @@
       <c r="E43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3">
         <v>600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11600</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -4032,8 +4125,8 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -4107,8 +4200,11 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4139,8 +4235,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4214,41 +4310,44 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E45" s="3">
         <v>19500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>16700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>11200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10000</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -4321,41 +4420,44 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>310700</v>
+      </c>
+      <c r="E46" s="3">
         <v>348100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>243300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>189300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>169200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>119400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>72900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>162200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>139600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>160000</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4428,41 +4530,44 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>228900</v>
+      </c>
+      <c r="E47" s="3">
         <v>213500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>223600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>208700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>207900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>202300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>208300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>206100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>208500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>255800</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -4535,91 +4640,94 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E48" s="3">
         <v>15100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>12200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3000</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>2800</v>
       </c>
       <c r="AE48" s="3">
         <v>2800</v>
@@ -4627,8 +4735,8 @@
       <c r="AF48" s="3">
         <v>2800</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>3</v>
+      <c r="AG48" s="3">
+        <v>2800</v>
       </c>
       <c r="AH48" s="3" t="s">
         <v>3</v>
@@ -4642,20 +4750,23 @@
       <c r="AK48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E49" s="3">
         <v>41900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>42500</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
         <v>0</v>
       </c>
@@ -4749,8 +4860,11 @@
       <c r="AK49" s="3">
         <v>0</v>
       </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +4970,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,88 +5080,91 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>86200</v>
+      </c>
+      <c r="E52" s="3">
         <v>85400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>83900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>70500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>53000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>50600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>52900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>50900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>50000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>49300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>13800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>12900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>12400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>9800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7200</v>
-      </c>
-      <c r="S52" s="3">
-        <v>7400</v>
       </c>
       <c r="T52" s="3">
         <v>7400</v>
       </c>
       <c r="U52" s="3">
+        <v>7400</v>
+      </c>
+      <c r="V52" s="3">
         <v>6800</v>
-      </c>
-      <c r="V52" s="3">
-        <v>3600</v>
       </c>
       <c r="W52" s="3">
         <v>3600</v>
       </c>
       <c r="X52" s="3">
+        <v>3600</v>
+      </c>
+      <c r="Y52" s="3">
         <v>4000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3600</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>3700</v>
       </c>
       <c r="AD52" s="3">
         <v>3700</v>
@@ -5053,11 +5173,11 @@
         <v>3700</v>
       </c>
       <c r="AF52" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AG52" s="3">
         <v>3600</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH52" s="3" t="s">
         <v>3</v>
       </c>
@@ -5070,8 +5190,11 @@
       <c r="AK52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,101 +5300,104 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3388700</v>
+      </c>
+      <c r="E54" s="3">
         <v>3349800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3206900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2560800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2438600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2324200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2226200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2272500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2227900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2245300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2123700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2009400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2154800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2122500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2055300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2169600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2151900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2091900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1876600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1879000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1822400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1507800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1427600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1311400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1234200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1123800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1105100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1072900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1067800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1017600</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5284,8 +5410,11 @@
       <c r="AK54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5452,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,101 +5492,102 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2940700</v>
+      </c>
+      <c r="E57" s="3">
         <v>2891300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2761900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2186200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2100400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2005700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1896000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1968000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1934400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1944400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>300</v>
-      </c>
-      <c r="P57" s="3">
-        <v>500</v>
       </c>
       <c r="Q57" s="3">
         <v>500</v>
       </c>
       <c r="R57" s="3">
+        <v>500</v>
+      </c>
+      <c r="S57" s="3">
         <v>800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2100</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>2000</v>
       </c>
       <c r="AB57" s="3">
         <v>2000</v>
       </c>
       <c r="AC57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AD57" s="3">
         <v>1600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1400</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5469,41 +5600,44 @@
       <c r="AK57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E58" s="3">
         <v>23600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>24000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>15000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>10900</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -5576,8 +5710,11 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5608,57 +5745,57 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>2400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5100</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5668,8 +5805,8 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG59" s="3">
-        <v>0</v>
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH59" s="3">
         <v>0</v>
@@ -5683,41 +5820,44 @@
       <c r="AK59" s="3">
         <v>0</v>
       </c>
+      <c r="AL59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2971900</v>
+      </c>
+      <c r="E60" s="3">
         <v>2924900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2795400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2195000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2107600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2012500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1916600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1973500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1938100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1957300</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -5790,8 +5930,11 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5799,31 +5942,31 @@
         <v>16000</v>
       </c>
       <c r="E61" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F61" s="3">
         <v>15900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>68200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>47900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>36700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>37900</v>
-      </c>
-      <c r="J61" s="3">
-        <v>37700</v>
       </c>
       <c r="K61" s="3">
         <v>37700</v>
       </c>
       <c r="L61" s="3">
+        <v>37700</v>
+      </c>
+      <c r="M61" s="3">
         <v>37200</v>
-      </c>
-      <c r="M61" s="3">
-        <v>12100</v>
       </c>
       <c r="N61" s="3">
         <v>12100</v>
@@ -5847,16 +5990,16 @@
         <v>12100</v>
       </c>
       <c r="U61" s="3">
+        <v>12100</v>
+      </c>
+      <c r="V61" s="3">
         <v>14000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>17500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>17400</v>
-      </c>
-      <c r="X61" s="3">
-        <v>15400</v>
       </c>
       <c r="Y61" s="3">
         <v>15400</v>
@@ -5877,14 +6020,14 @@
         <v>15400</v>
       </c>
       <c r="AE61" s="3">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
         <v>15400</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
@@ -5897,41 +6040,44 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E62" s="3">
         <v>39400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>40500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>17500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>15200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>15500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>16900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>18400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16300</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -6004,8 +6150,11 @@
       <c r="AK62" s="3">
         <v>0</v>
       </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6260,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6218,8 +6370,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,101 +6480,104 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3008600</v>
+      </c>
+      <c r="E66" s="3">
         <v>2980200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2851800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2280700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2170700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2064800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1971300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2029600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1990400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2010800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1899600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1795400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1947500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1921000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1857400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1980500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1974600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1924800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1717300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1729700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1680300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1371800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1294300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1183600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1111000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1005200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>990500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>966200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>980800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>934200</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6432,8 +6590,11 @@
       <c r="AK66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6632,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6740,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +6850,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6792,8 +6960,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,101 +7070,104 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>261100</v>
+      </c>
+      <c r="E72" s="3">
         <v>249900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>237800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>233000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>225800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>218700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>213300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>206000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>197500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>191100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>182400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>174900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>164800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>153900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>144500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>135900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>125400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>115800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>106900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>97600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>89200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>84400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>81600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>77100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>72900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>68900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>65700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>62500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>59300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>56200</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH72" s="3" t="s">
         <v>3</v>
       </c>
@@ -7006,8 +7180,11 @@
       <c r="AK72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7290,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7400,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,101 +7510,104 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>380000</v>
+      </c>
+      <c r="E76" s="3">
         <v>369600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>355100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>280100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>267900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>259500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>254900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>242900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>237400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>234500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>224000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>214000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>207300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>201500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>197900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>189100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>177200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>167000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>159300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>149400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>142100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>136100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>133300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>127800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>123100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>118600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>114600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>106700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>87000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>83400</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7434,8 +7620,11 @@
       <c r="AK76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,227 +7730,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2" t="s">
+      <c r="AL80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E81" s="3">
         <v>13900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>8200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>9000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>9800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>9700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>9000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>11100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>11500</v>
-      </c>
-      <c r="P81" s="3">
-        <v>10200</v>
       </c>
       <c r="Q81" s="3">
         <v>10200</v>
       </c>
       <c r="R81" s="3">
+        <v>10200</v>
+      </c>
+      <c r="S81" s="3">
         <v>11200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>9600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>9000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>9700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>8400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>5100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>4000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>6100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>3000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1900</v>
       </c>
-      <c r="AK81" s="3" t="s">
+      <c r="AL81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,25 +7997,26 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
         <v>300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>300</v>
       </c>
       <c r="I83" s="3">
         <v>300</v>
@@ -7826,49 +8025,49 @@
         <v>300</v>
       </c>
       <c r="K83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="L83" s="3">
         <v>400</v>
       </c>
       <c r="M83" s="3">
+        <v>400</v>
+      </c>
+      <c r="N83" s="3">
         <v>-700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>300</v>
-      </c>
-      <c r="O83" s="3">
-        <v>400</v>
       </c>
       <c r="P83" s="3">
         <v>400</v>
       </c>
       <c r="Q83" s="3">
+        <v>400</v>
+      </c>
+      <c r="R83" s="3">
         <v>-500</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="T83" s="3">
         <v>500</v>
       </c>
       <c r="U83" s="3">
+        <v>500</v>
+      </c>
+      <c r="V83" s="3">
         <v>-600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>500</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>300</v>
       </c>
       <c r="Z83" s="3">
         <v>300</v>
@@ -7883,31 +8082,34 @@
         <v>300</v>
       </c>
       <c r="AD83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE83" s="3">
         <v>200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>300</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH83" s="3">
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI83" s="3">
         <v>200</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8215,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8325,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8435,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8545,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,115 +8655,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E89" s="3">
         <v>22600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>25900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>12900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>22500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>8400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>15800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>20300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>29500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>26400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>21500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>54600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>41300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-8900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-30100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>8200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-14800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-21500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>10400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>15100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>12900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>6800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>4700</v>
       </c>
-      <c r="AI89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,77 +8807,78 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-800</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3">
         <v>400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-2300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-700</v>
       </c>
       <c r="O91" s="3">
         <v>-700</v>
       </c>
       <c r="P91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V91" s="3">
         <v>100</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
@@ -8667,35 +8888,38 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-700</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>-400</v>
       </c>
       <c r="AG91" s="3">
         <v>-400</v>
       </c>
       <c r="AH91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-300</v>
       </c>
-      <c r="AI91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9025,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,115 +9135,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-60300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-61100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-63100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-83700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-65500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-57600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-39100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-26300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-58700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-68000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-77700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-108800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>56100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-45900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-14500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-85300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-92600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-86000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-34000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-249500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-16000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-57300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-81700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-42500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-6400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-43400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-33800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-32000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-12000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-16700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-32300</v>
       </c>
-      <c r="AI94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,8 +9287,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9066,10 +9300,10 @@
         <v>1700</v>
       </c>
       <c r="F96" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G96" s="3">
         <v>1400</v>
-      </c>
-      <c r="G96" s="3">
-        <v>1100</v>
       </c>
       <c r="H96" s="3">
         <v>1100</v>
@@ -9081,25 +9315,25 @@
         <v>1100</v>
       </c>
       <c r="K96" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L96" s="3">
         <v>800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>900</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-800</v>
       </c>
       <c r="N96" s="3">
         <v>-800</v>
       </c>
       <c r="O96" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="P96" s="3">
         <v>-700</v>
       </c>
       <c r="Q96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -9161,8 +9395,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9505,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9615,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,115 +9725,121 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>45100</v>
+      </c>
+      <c r="E100" s="3">
         <v>127200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>85800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>104400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>103900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>92300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-59200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>30600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-22700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>108300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>105300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-151900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>25600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>65100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-124300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>54400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>209100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-14000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>48700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>304400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>73000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>109700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>72100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>105200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>8300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>27000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>3000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>33300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-10600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>22700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>16600</v>
       </c>
-      <c r="AI100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9621,8 +9870,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9696,111 +9945,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="E102" s="3">
         <v>88700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>48600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>20200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>51300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>31200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-92200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>26800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-21000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>60000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>43400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-213800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-62900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>130400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-140600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>15300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-9400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>171100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-58600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>5800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>24800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>60000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>59700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-24500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>41200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>3600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-28000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>16400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-9700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>12700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-10900</v>
       </c>
-      <c r="AI102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CBNK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CBNK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="92">
   <si>
     <t>CBNK</t>
   </si>
@@ -656,280 +656,286 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AN102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2" t="s">
+      <c r="AN7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>58800</v>
+      </c>
+      <c r="E8" s="3">
         <v>58200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>56700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>56400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>50900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>41200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>40400</v>
-      </c>
-      <c r="J8" s="3">
-        <v>38100</v>
       </c>
       <c r="K8" s="3">
         <v>38100</v>
       </c>
       <c r="L8" s="3">
+        <v>38100</v>
+      </c>
+      <c r="M8" s="3">
         <v>40800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>39200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>38900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>41300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>38300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>36600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>34400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>33800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>33500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>29300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>26600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>28300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>25200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>22000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>21700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>21200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>22400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>20300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>18300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>18200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>17400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>33400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>16700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>14700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>15000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>14200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>12800</v>
       </c>
-      <c r="AM8" s="3" t="s">
+      <c r="AN8" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1041,47 +1047,50 @@
       <c r="AM9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>58800</v>
+      </c>
+      <c r="E10" s="3">
         <v>58200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>56700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>56400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>50900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>41200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>40400</v>
-      </c>
-      <c r="J10" s="3">
-        <v>38100</v>
       </c>
       <c r="K10" s="3">
         <v>38100</v>
       </c>
       <c r="L10" s="3">
+        <v>38100</v>
+      </c>
+      <c r="M10" s="3">
         <v>40800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>39200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>38900</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1154,8 +1163,11 @@
       <c r="AM10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1195,8 +1207,9 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1308,8 +1321,11 @@
       <c r="AM12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1421,35 +1437,38 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>5200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>700</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1459,8 +1478,8 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1534,25 +1553,28 @@
       <c r="AM14" s="3">
         <v>0</v>
       </c>
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E15" s="3">
         <v>600</v>
       </c>
       <c r="F15" s="3">
+        <v>600</v>
+      </c>
+      <c r="G15" s="3">
         <v>500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>800</v>
-      </c>
-      <c r="H15" s="3">
-        <v>100</v>
       </c>
       <c r="I15" s="3">
         <v>100</v>
@@ -1573,7 +1595,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1647,8 +1669,11 @@
       <c r="AM15" s="3">
         <v>0</v>
       </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1685,234 +1710,241 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E17" s="3">
         <v>37700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>38200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>36800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>34900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>29200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>29400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>28800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>26900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>28000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>29600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>26200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2300</v>
       </c>
-      <c r="AM17" s="3" t="s">
+      <c r="AN17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E18" s="3">
         <v>20600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>18500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>19600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>16000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>12000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>11000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>11200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>12800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>12700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>32800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>35400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>33400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>32400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>31600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>31100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>26800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>23900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>25700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>22100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>18600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>17600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>15900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>17200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>15900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>14600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>14400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>14000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>27300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>13900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>11800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>12300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>11700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>10500</v>
       </c>
-      <c r="AM18" s="3" t="s">
+      <c r="AN18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1952,19 +1984,20 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
@@ -1972,11 +2005,11 @@
       <c r="H20" s="3">
         <v>0</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1984,202 +2017,208 @@
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-21100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-20900</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-18800</v>
       </c>
       <c r="R20" s="3">
         <v>-18800</v>
       </c>
       <c r="S20" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="T20" s="3">
         <v>-17900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-16000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-13700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-11800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-12700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-12100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-13600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-9300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-11100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-10300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-10200</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>-9600</v>
       </c>
       <c r="AF20" s="3">
         <v>-9600</v>
       </c>
       <c r="AG20" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-18700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-9600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-10400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-7300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-7000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-7500</v>
       </c>
-      <c r="AM20" s="3" t="s">
+      <c r="AN20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E21" s="3">
         <v>21200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>19100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>20000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>16800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>12100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>11100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>11300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>12900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>12700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>10900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>14800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>15000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>14000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>13200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>15100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>13500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>12600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>12500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>12100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>6900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>6900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>6400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>5900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>5100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>9200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>4600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>5200</v>
       </c>
-      <c r="AK21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL21" s="3">
+      <c r="AL21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="3">
         <v>3300</v>
       </c>
-      <c r="AM21" s="3" t="s">
+      <c r="AN21" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2216,8 +2255,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2291,234 +2330,243 @@
       <c r="AM22" s="3">
         <v>0</v>
       </c>
+      <c r="AN22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E23" s="3">
         <v>19900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>17100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>18300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>10800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>11500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>11200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>12800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>9600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>12700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>11600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>14400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>14600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>13600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>13700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>15100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>13000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>12100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>13000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>11600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>6500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>5600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>8700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>4300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>5000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>4700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>3000</v>
       </c>
-      <c r="AM23" s="3" t="s">
+      <c r="AN23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E24" s="3">
         <v>4800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1100</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>1600</v>
       </c>
       <c r="AB24" s="3">
         <v>1600</v>
       </c>
       <c r="AC24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AD24" s="3">
         <v>1500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>1200</v>
       </c>
-      <c r="AM24" s="3" t="s">
+      <c r="AN24" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2630,234 +2678,243 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E26" s="3">
         <v>15100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>13100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>13900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>8700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>9000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>9700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>9000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>11100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>11500</v>
-      </c>
-      <c r="R26" s="3">
-        <v>10200</v>
       </c>
       <c r="S26" s="3">
         <v>10200</v>
       </c>
       <c r="T26" s="3">
+        <v>10200</v>
+      </c>
+      <c r="U26" s="3">
         <v>11200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>9600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>9000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>9700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>8400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>5100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>6100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>3000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1900</v>
       </c>
-      <c r="AM26" s="3" t="s">
+      <c r="AN26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E27" s="3">
         <v>15100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>13100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>13900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>8700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>9000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>9800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>9700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>9000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>11100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>11500</v>
-      </c>
-      <c r="R27" s="3">
-        <v>10200</v>
       </c>
       <c r="S27" s="3">
         <v>10200</v>
       </c>
       <c r="T27" s="3">
+        <v>10200</v>
+      </c>
+      <c r="U27" s="3">
         <v>11200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>9600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>9000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>9700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>8400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>5100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>4000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>6100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>3000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>3000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>2900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1900</v>
       </c>
-      <c r="AM27" s="3" t="s">
+      <c r="AN27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2969,8 +3026,11 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3049,17 +3109,17 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>3</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>3</v>
+      <c r="AE29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>3</v>
@@ -3067,12 +3127,12 @@
       <c r="AH29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>3</v>
       </c>
@@ -3082,8 +3142,11 @@
       <c r="AM29" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN29" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3195,8 +3258,11 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3308,19 +3374,22 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
@@ -3328,11 +3397,11 @@
       <c r="H32" s="3">
         <v>0</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -3340,202 +3409,208 @@
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>21100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>20900</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>18800</v>
       </c>
       <c r="R32" s="3">
         <v>18800</v>
       </c>
       <c r="S32" s="3">
+        <v>18800</v>
+      </c>
+      <c r="T32" s="3">
         <v>17900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>16000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>13700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>11800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>12700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>10500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>12100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>13600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>9300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>11100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>10300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>10200</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>9600</v>
       </c>
       <c r="AF32" s="3">
         <v>9600</v>
       </c>
       <c r="AG32" s="3">
+        <v>9600</v>
+      </c>
+      <c r="AH32" s="3">
         <v>18700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>9600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>10400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>7300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>7000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>7500</v>
       </c>
-      <c r="AM32" s="3" t="s">
+      <c r="AN32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E33" s="3">
         <v>15100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>13100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>13900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>8700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>9000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>9800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>9700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>9000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>11100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>11500</v>
-      </c>
-      <c r="R33" s="3">
-        <v>10200</v>
       </c>
       <c r="S33" s="3">
         <v>10200</v>
       </c>
       <c r="T33" s="3">
+        <v>10200</v>
+      </c>
+      <c r="U33" s="3">
         <v>11200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>9600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>9000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>9700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>8400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>4500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>4000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>6100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>3000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>3000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>2900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1900</v>
       </c>
-      <c r="AM33" s="3" t="s">
+      <c r="AN33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3647,239 +3722,248 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E35" s="3">
         <v>15100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>13100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>13900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>8700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>9000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>9800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>9700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>9000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>11100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>11500</v>
-      </c>
-      <c r="R35" s="3">
-        <v>10200</v>
       </c>
       <c r="S35" s="3">
         <v>10200</v>
       </c>
       <c r="T35" s="3">
+        <v>10200</v>
+      </c>
+      <c r="U35" s="3">
         <v>11200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>9600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>9000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>9700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>8400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>4500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>4000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>6100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>3000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>3000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>2900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1900</v>
       </c>
-      <c r="AM35" s="3" t="s">
+      <c r="AN35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2" t="s">
+      <c r="AN38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3919,8 +4003,9 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3960,107 +4045,108 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>255600</v>
+      </c>
+      <c r="E41" s="3">
         <v>188900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>274600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>294000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>205300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>156700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>136500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>85200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>54000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>146200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>119300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>140400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>20000</v>
-      </c>
-      <c r="P41" s="3">
-        <v>14800</v>
       </c>
       <c r="Q41" s="3">
         <v>14800</v>
       </c>
       <c r="R41" s="3">
+        <v>14800</v>
+      </c>
+      <c r="S41" s="3">
         <v>15000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>42900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>23700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>19700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>22700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>18500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>20100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>15600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>10500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>11100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>12300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>11600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>10400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>11000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>9800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>9600</v>
       </c>
-      <c r="AI41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ41" s="3" t="s">
         <v>3</v>
       </c>
@@ -4073,8 +4159,11 @@
       <c r="AM41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4112,68 +4201,68 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>60500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>22500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>236400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>299100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>140700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>300600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>289200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>295600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>128500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>185400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>184100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>165300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>104300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>44000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>67300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>26700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>24300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>29700</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>58900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>35500</v>
       </c>
-      <c r="AI42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ42" s="3" t="s">
         <v>3</v>
       </c>
@@ -4186,8 +4275,11 @@
       <c r="AM42" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN42" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4203,18 +4295,18 @@
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3">
         <v>600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11600</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -4224,8 +4316,8 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -4299,13 +4391,16 @@
       <c r="AM43" s="3">
         <v>0</v>
       </c>
+      <c r="AN43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>3</v>
+      <c r="D44" s="3">
+        <v>3900</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>3</v>
@@ -4337,8 +4432,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4412,47 +4507,50 @@
       <c r="AM44" s="3">
         <v>0</v>
       </c>
+      <c r="AN44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E45" s="3">
         <v>19000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>15100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>19500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>16700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>12300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>11500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10000</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
@@ -4525,47 +4623,50 @@
       <c r="AM45" s="3">
         <v>0</v>
       </c>
+      <c r="AN45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>301900</v>
+      </c>
+      <c r="E46" s="3">
         <v>227600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>310700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>348100</v>
       </c>
-      <c r="G46" s="3">
-        <v>243300</v>
-      </c>
       <c r="H46" s="3">
+        <v>239100</v>
+      </c>
+      <c r="I46" s="3">
         <v>189300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>169200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>119400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>72900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>162200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>139600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>160000</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -4638,47 +4739,50 @@
       <c r="AM46" s="3">
         <v>0</v>
       </c>
+      <c r="AN46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>230100</v>
+      </c>
+      <c r="E47" s="3">
         <v>232600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>228900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>213500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>223600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>208700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>207900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>202300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>208300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>206100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>208500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>255800</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
@@ -4751,97 +4855,100 @@
       <c r="AM47" s="3">
         <v>0</v>
       </c>
+      <c r="AN47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E48" s="3">
         <v>15300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>15500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>12200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3000</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>2800</v>
       </c>
       <c r="AG48" s="3">
         <v>2800</v>
@@ -4849,8 +4956,8 @@
       <c r="AH48" s="3">
         <v>2800</v>
       </c>
-      <c r="AI48" s="3" t="s">
-        <v>3</v>
+      <c r="AI48" s="3">
+        <v>2800</v>
       </c>
       <c r="AJ48" s="3" t="s">
         <v>3</v>
@@ -4864,26 +4971,29 @@
       <c r="AM48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E49" s="3">
         <v>43100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>40000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>41900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>42500</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
@@ -4977,8 +5087,11 @@
       <c r="AM49" s="3">
         <v>0</v>
       </c>
+      <c r="AN49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5090,8 +5203,11 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5203,94 +5319,97 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>96800</v>
+      </c>
+      <c r="E52" s="3">
         <v>87100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>86200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>85400</v>
       </c>
-      <c r="G52" s="3">
-        <v>83900</v>
-      </c>
       <c r="H52" s="3">
+        <v>88100</v>
+      </c>
+      <c r="I52" s="3">
         <v>70500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>53000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>50600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>52900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>50900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>50000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>49300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>13800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>14000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>12900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>12400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>9800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7200</v>
-      </c>
-      <c r="U52" s="3">
-        <v>7400</v>
       </c>
       <c r="V52" s="3">
         <v>7400</v>
       </c>
       <c r="W52" s="3">
+        <v>7400</v>
+      </c>
+      <c r="X52" s="3">
         <v>6800</v>
-      </c>
-      <c r="X52" s="3">
-        <v>3600</v>
       </c>
       <c r="Y52" s="3">
         <v>3600</v>
       </c>
       <c r="Z52" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AA52" s="3">
         <v>4000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3600</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>3700</v>
       </c>
       <c r="AF52" s="3">
         <v>3700</v>
@@ -5299,11 +5418,11 @@
         <v>3700</v>
       </c>
       <c r="AH52" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AI52" s="3">
         <v>3600</v>
       </c>
-      <c r="AI52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ52" s="3" t="s">
         <v>3</v>
       </c>
@@ -5316,8 +5435,11 @@
       <c r="AM52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5429,107 +5551,110 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3606200</v>
+      </c>
+      <c r="E54" s="3">
         <v>3389400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3388700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3349800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3206900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2560800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2438600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2324200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2226200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2272500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2227900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2245300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2123700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2009400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2154800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2122500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2055300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2169600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2151900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2091900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1876600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1879000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1822400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1507800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1427600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1311400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1234200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1123800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1105100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1072900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1067800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1017600</v>
       </c>
-      <c r="AI54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5542,8 +5667,11 @@
       <c r="AM54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5583,8 +5711,9 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5624,107 +5753,108 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3093200</v>
+      </c>
+      <c r="E57" s="3">
         <v>2912100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2940700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2891300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2761900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2186200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2100400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2005700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1896000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1968000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1934400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1944400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>300</v>
-      </c>
-      <c r="R57" s="3">
-        <v>500</v>
       </c>
       <c r="S57" s="3">
         <v>500</v>
       </c>
       <c r="T57" s="3">
+        <v>500</v>
+      </c>
+      <c r="U57" s="3">
         <v>800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2100</v>
-      </c>
-      <c r="AC57" s="3">
-        <v>2000</v>
       </c>
       <c r="AD57" s="3">
         <v>2000</v>
       </c>
       <c r="AE57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AF57" s="3">
         <v>1600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1400</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5737,47 +5867,50 @@
       <c r="AM57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E58" s="3">
         <v>22500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>23100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>23600</v>
       </c>
-      <c r="G58" s="3">
-        <v>24000</v>
-      </c>
       <c r="H58" s="3">
+        <v>22000</v>
+      </c>
+      <c r="I58" s="3">
         <v>200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>15000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10900</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -5850,8 +5983,11 @@
       <c r="AM58" s="3">
         <v>0</v>
       </c>
+      <c r="AN58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5888,57 +6024,57 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3">
         <v>2400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>5100</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5948,8 +6084,8 @@
       <c r="AH59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AI59" s="3">
-        <v>0</v>
+      <c r="AI59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AJ59" s="3">
         <v>0</v>
@@ -5963,47 +6099,50 @@
       <c r="AM59" s="3">
         <v>0</v>
       </c>
+      <c r="AN59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3153900</v>
+      </c>
+      <c r="E60" s="3">
         <v>2942600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2971900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2924900</v>
       </c>
-      <c r="G60" s="3">
-        <v>2795400</v>
-      </c>
       <c r="H60" s="3">
+        <v>2793300</v>
+      </c>
+      <c r="I60" s="3">
         <v>2195000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2107600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2012500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1916600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1973500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1938100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1957300</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -6076,46 +6215,49 @@
       <c r="AM60" s="3">
         <v>0</v>
       </c>
+      <c r="AN60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E61" s="3">
         <v>16400</v>
-      </c>
-      <c r="E61" s="3">
-        <v>16000</v>
       </c>
       <c r="F61" s="3">
         <v>16000</v>
       </c>
       <c r="G61" s="3">
-        <v>15900</v>
+        <v>16000</v>
       </c>
       <c r="H61" s="3">
+        <v>17900</v>
+      </c>
+      <c r="I61" s="3">
         <v>68200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>47900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>36700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>37900</v>
-      </c>
-      <c r="L61" s="3">
-        <v>37700</v>
       </c>
       <c r="M61" s="3">
         <v>37700</v>
       </c>
       <c r="N61" s="3">
+        <v>37700</v>
+      </c>
+      <c r="O61" s="3">
         <v>37200</v>
-      </c>
-      <c r="O61" s="3">
-        <v>12100</v>
       </c>
       <c r="P61" s="3">
         <v>12100</v>
@@ -6139,16 +6281,16 @@
         <v>12100</v>
       </c>
       <c r="W61" s="3">
+        <v>12100</v>
+      </c>
+      <c r="X61" s="3">
         <v>14000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>17500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>17400</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>15400</v>
       </c>
       <c r="AA61" s="3">
         <v>15400</v>
@@ -6169,14 +6311,14 @@
         <v>15400</v>
       </c>
       <c r="AG61" s="3">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
         <v>15400</v>
       </c>
-      <c r="AI61" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
@@ -6189,47 +6331,50 @@
       <c r="AM61" s="3">
         <v>0</v>
       </c>
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>45900</v>
+      </c>
+      <c r="E62" s="3">
         <v>35600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>20600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>39400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>40500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>17500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>15200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>15500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>18400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>14700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16300</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
@@ -6302,8 +6447,11 @@
       <c r="AM62" s="3">
         <v>0</v>
       </c>
+      <c r="AN62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6415,8 +6563,11 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6528,8 +6679,11 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6641,107 +6795,110 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3204500</v>
+      </c>
+      <c r="E66" s="3">
         <v>2994700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3008600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2980200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2851800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2280700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2170700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2064800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1971300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2029600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1990400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2010800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1899600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1795400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1947500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1921000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1857400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1980500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1974600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1924800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1717300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1729700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1680300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1371800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1294300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1183600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1111000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1005200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>990500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>966200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>980800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>934200</v>
       </c>
-      <c r="AI66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6754,8 +6911,11 @@
       <c r="AM66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6795,8 +6955,9 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6908,8 +7069,11 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7021,8 +7185,11 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7134,8 +7301,11 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7247,107 +7417,110 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>292700</v>
+      </c>
+      <c r="E72" s="3">
         <v>274000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>261100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>249900</v>
       </c>
-      <c r="G72" s="3">
-        <v>237800</v>
-      </c>
       <c r="H72" s="3">
+        <v>242900</v>
+      </c>
+      <c r="I72" s="3">
         <v>233000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>225800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>218700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>213300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>206000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>197500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>191100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>182400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>174900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>164800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>153900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>144500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>135900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>125400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>115800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>106900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>97600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>89200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>84400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>81600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>77100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>72900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>68900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>65700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>62500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>59300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>56200</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ72" s="3" t="s">
         <v>3</v>
       </c>
@@ -7360,8 +7533,11 @@
       <c r="AM72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7473,8 +7649,11 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7586,8 +7765,11 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7699,107 +7881,110 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>401800</v>
+      </c>
+      <c r="E76" s="3">
         <v>394800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>380000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>369600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>355100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>280100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>267900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>259500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>254900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>242900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>237400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>234500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>224000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>214000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>207300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>201500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>197900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>189100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>177200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>167000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>159300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>149400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>142100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>136100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>133300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>127800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>123100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>118600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>114600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>106700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>87000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>83400</v>
       </c>
-      <c r="AI76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7812,8 +7997,11 @@
       <c r="AM76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7925,239 +8113,248 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2" t="s">
+      <c r="AN80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E81" s="3">
         <v>15100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>13100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>13900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>8700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>9000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>9800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>9700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>9000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>11100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>11500</v>
-      </c>
-      <c r="R81" s="3">
-        <v>10200</v>
       </c>
       <c r="S81" s="3">
         <v>10200</v>
       </c>
       <c r="T81" s="3">
+        <v>10200</v>
+      </c>
+      <c r="U81" s="3">
         <v>11200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>9600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>9000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>9700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>8400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>4500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>4000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>6100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>3000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>3000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>2900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1900</v>
       </c>
-      <c r="AM81" s="3" t="s">
+      <c r="AN81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8197,31 +8394,32 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E83" s="3">
         <v>-100</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
       <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
         <v>300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>300</v>
       </c>
       <c r="K83" s="3">
         <v>300</v>
@@ -8230,49 +8428,49 @@
         <v>300</v>
       </c>
       <c r="M83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="N83" s="3">
         <v>400</v>
       </c>
       <c r="O83" s="3">
+        <v>400</v>
+      </c>
+      <c r="P83" s="3">
         <v>-700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>300</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>400</v>
       </c>
       <c r="R83" s="3">
         <v>400</v>
       </c>
       <c r="S83" s="3">
+        <v>400</v>
+      </c>
+      <c r="T83" s="3">
         <v>-500</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
       <c r="U83" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="V83" s="3">
         <v>500</v>
       </c>
       <c r="W83" s="3">
+        <v>500</v>
+      </c>
+      <c r="X83" s="3">
         <v>-600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>500</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>300</v>
       </c>
       <c r="AB83" s="3">
         <v>300</v>
@@ -8287,31 +8485,34 @@
         <v>300</v>
       </c>
       <c r="AF83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG83" s="3">
         <v>200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>300</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ83" s="3">
+      <c r="AJ83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK83" s="3">
         <v>200</v>
       </c>
-      <c r="AK83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AM83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8423,8 +8624,11 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8536,8 +8740,11 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8649,8 +8856,11 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8762,8 +8972,11 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8875,121 +9088,127 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E89" s="3">
         <v>32900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>22600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>25900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>12900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>22500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>8400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>10400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>15800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>20300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>9200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>29500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>26400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>21500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>54600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>41300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-8900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-30100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>8200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-14800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-21500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>10400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>15100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>12900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>6800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>4700</v>
       </c>
-      <c r="AK89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AM89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9029,83 +9248,84 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-800</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3">
         <v>400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-2300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-700</v>
       </c>
       <c r="Q91" s="3">
         <v>-700</v>
       </c>
       <c r="R91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X91" s="3">
         <v>100</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
@@ -9115,35 +9335,38 @@
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-700</v>
-      </c>
-      <c r="AH91" s="3">
-        <v>-400</v>
       </c>
       <c r="AI91" s="3">
         <v>-400</v>
       </c>
       <c r="AJ91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-300</v>
       </c>
-      <c r="AK91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AM91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9255,8 +9478,11 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9368,121 +9594,127 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-141400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-88100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-60300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-61100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-63100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-83700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-65500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-57600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-39100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-26300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-58700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-68000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-77700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-108800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>56100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-45900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-14500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-85300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-92600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-86000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-34000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-249500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-57300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-81700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-42500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-6400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-43400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-33800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-32000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-12000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-16700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-32300</v>
       </c>
-      <c r="AK94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AM94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9522,8 +9754,9 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9531,7 +9764,7 @@
         <v>2000</v>
       </c>
       <c r="E96" s="3">
-        <v>1700</v>
+        <v>2000</v>
       </c>
       <c r="F96" s="3">
         <v>1700</v>
@@ -9540,10 +9773,10 @@
         <v>1700</v>
       </c>
       <c r="H96" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I96" s="3">
         <v>1400</v>
-      </c>
-      <c r="I96" s="3">
-        <v>1100</v>
       </c>
       <c r="J96" s="3">
         <v>1100</v>
@@ -9555,25 +9788,25 @@
         <v>1100</v>
       </c>
       <c r="M96" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N96" s="3">
         <v>800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>900</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-800</v>
       </c>
       <c r="P96" s="3">
         <v>-800</v>
       </c>
       <c r="Q96" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="R96" s="3">
         <v>-700</v>
       </c>
       <c r="S96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="T96" s="3">
         <v>0</v>
@@ -9635,8 +9868,11 @@
       <c r="AM96" s="3">
         <v>0</v>
       </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9748,8 +9984,11 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9861,8 +10100,11 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9974,121 +10216,127 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>189700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-30600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>45100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>127200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>85800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>104400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>103900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>92300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-59200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>30600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-22700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>108300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>105300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-151900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>25600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>65100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-124300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>3400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>54400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>209100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-14000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>48700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>304400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>73000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>109700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>72100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>105200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>8300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>27000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>3000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>33300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-10600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>22700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>16600</v>
       </c>
-      <c r="AK100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AM100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10125,8 +10373,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10200,117 +10448,123 @@
       <c r="AM101" s="3">
         <v>0</v>
       </c>
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>66700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-85700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-19400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>88700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>48600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>20200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>51300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>31200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-92200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>26800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-21000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>60000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>43400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-213800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-62900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>130400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-140600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>15300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-9400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>171100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-58600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>5800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>24800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>60000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>59700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-24500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>41200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>3600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-28000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>16400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-9700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>12700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-10900</v>
       </c>
-      <c r="AK102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AM102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CBNK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CBNK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="92">
   <si>
     <t>CBNK</t>
   </si>
@@ -656,286 +656,293 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2" t="s">
+      <c r="AO7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E8" s="3">
         <v>58800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>58200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>56700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>56400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>50900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>41200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>40400</v>
-      </c>
-      <c r="K8" s="3">
-        <v>38100</v>
       </c>
       <c r="L8" s="3">
         <v>38100</v>
       </c>
       <c r="M8" s="3">
+        <v>38100</v>
+      </c>
+      <c r="N8" s="3">
         <v>40800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>39200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>38900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>41300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>38300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>36600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>34400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>33800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>33500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>29300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>26600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>28300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>25200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>22000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>21700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>21200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>22400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>20300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>18300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>18200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>17400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>33400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>16700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>14700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>15000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>14200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>12800</v>
       </c>
-      <c r="AN8" s="3" t="s">
+      <c r="AO8" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1050,50 +1057,53 @@
       <c r="AN9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E10" s="3">
         <v>58800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>58200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>56700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>56400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>50900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>41200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>40400</v>
-      </c>
-      <c r="K10" s="3">
-        <v>38100</v>
       </c>
       <c r="L10" s="3">
         <v>38100</v>
       </c>
       <c r="M10" s="3">
+        <v>38100</v>
+      </c>
+      <c r="N10" s="3">
         <v>40800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>39200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>38900</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1166,8 +1176,11 @@
       <c r="AN10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1208,8 +1221,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1324,8 +1338,11 @@
       <c r="AN12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,38 +1457,41 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>5200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>700</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1481,8 +1501,8 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1556,28 +1576,31 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E15" s="3">
         <v>800</v>
-      </c>
-      <c r="E15" s="3">
-        <v>600</v>
       </c>
       <c r="F15" s="3">
         <v>600</v>
       </c>
       <c r="G15" s="3">
+        <v>600</v>
+      </c>
+      <c r="H15" s="3">
         <v>500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>800</v>
-      </c>
-      <c r="I15" s="3">
-        <v>100</v>
       </c>
       <c r="J15" s="3">
         <v>100</v>
@@ -1598,7 +1621,7 @@
         <v>100</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1672,8 +1695,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1737,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E17" s="3">
         <v>39100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>37700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>38200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>36800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>34900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>29200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>29400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>28800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>26900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>28000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>29600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>26200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2300</v>
       </c>
-      <c r="AN17" s="3" t="s">
+      <c r="AO17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E18" s="3">
         <v>19700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>20600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>18500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>19600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>16000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>12000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>11000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>12800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>12700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>32800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>35400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>33400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>32400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>31600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>31100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>26800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>23900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>25700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>22100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>18600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>17600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>15900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>17200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>15900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>14600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>14400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>14000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>27300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>13900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>11800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>12300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>11700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>10500</v>
       </c>
-      <c r="AN18" s="3" t="s">
+      <c r="AO18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,34 +2018,35 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -2020,205 +2054,211 @@
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-21100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-20900</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-18800</v>
       </c>
       <c r="S20" s="3">
         <v>-18800</v>
       </c>
       <c r="T20" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="U20" s="3">
         <v>-17900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-16000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-13700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-11800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-12700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-10500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-12100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-13600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-9300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-11100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-10300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-10200</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>-9600</v>
       </c>
       <c r="AG20" s="3">
         <v>-9600</v>
       </c>
       <c r="AH20" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-18700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-9600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-10400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-7300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-7000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-7500</v>
       </c>
-      <c r="AN20" s="3" t="s">
+      <c r="AO20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E21" s="3">
         <v>20500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>21200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>19100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>20000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>16800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>12100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>11100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>11300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>12900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>12700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>10900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>14800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>15000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>14000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>13200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>15100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>13500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>12600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>12500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>12100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>6900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>6900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>6400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>5900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>5100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>4600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>9200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>4600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>5200</v>
       </c>
-      <c r="AL21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AM21" s="3">
+      <c r="AM21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN21" s="3">
         <v>3300</v>
       </c>
-      <c r="AN21" s="3" t="s">
+      <c r="AO21" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2258,8 +2298,8 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2333,240 +2373,249 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E23" s="3">
         <v>19700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>19900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>17100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>18300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>10800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>11500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>10900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>11200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>12800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>9600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>12700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>11600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>14400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>14600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>13600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>13700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>15100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>13000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>12100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>13000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>11600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>6500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>6100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>5600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>4300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>8700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>4300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>5000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>4700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>3000</v>
       </c>
-      <c r="AN23" s="3" t="s">
+      <c r="AO23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E24" s="3">
         <v>4600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1100</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>1600</v>
       </c>
       <c r="AC24" s="3">
         <v>1600</v>
       </c>
       <c r="AD24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AE24" s="3">
         <v>1500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>1800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>1200</v>
       </c>
-      <c r="AN24" s="3" t="s">
+      <c r="AO24" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,240 +2730,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E26" s="3">
         <v>15000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>15100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>13100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>13900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>9800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>9700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>9000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>11100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>11500</v>
-      </c>
-      <c r="S26" s="3">
-        <v>10200</v>
       </c>
       <c r="T26" s="3">
         <v>10200</v>
       </c>
       <c r="U26" s="3">
+        <v>10200</v>
+      </c>
+      <c r="V26" s="3">
         <v>11200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>9600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>9000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>9700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>8400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>5100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>6100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>3000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>2900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1900</v>
       </c>
-      <c r="AN26" s="3" t="s">
+      <c r="AO26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E27" s="3">
         <v>15000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>15100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>13100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>13900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>9000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>9800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>9700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>9000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>11100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>11500</v>
-      </c>
-      <c r="S27" s="3">
-        <v>10200</v>
       </c>
       <c r="T27" s="3">
         <v>10200</v>
       </c>
       <c r="U27" s="3">
+        <v>10200</v>
+      </c>
+      <c r="V27" s="3">
         <v>11200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>9600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>9000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>9700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>8400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>5100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>4500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>4000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>6100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>3000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>2900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1900</v>
       </c>
-      <c r="AN27" s="3" t="s">
+      <c r="AO27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3087,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3112,17 +3173,17 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>3</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>3</v>
+      <c r="AF29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>3</v>
@@ -3130,12 +3191,12 @@
       <c r="AI29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-1400</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>3</v>
       </c>
@@ -3145,8 +3206,11 @@
       <c r="AN29" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3325,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,34 +3444,37 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -3412,205 +3482,211 @@
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>21100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>20900</v>
-      </c>
-      <c r="R32" s="3">
-        <v>18800</v>
       </c>
       <c r="S32" s="3">
         <v>18800</v>
       </c>
       <c r="T32" s="3">
+        <v>18800</v>
+      </c>
+      <c r="U32" s="3">
         <v>17900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>16000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>13700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>11800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>12700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>10500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>12100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>13600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>9300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>11100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>10300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>10200</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>9600</v>
       </c>
       <c r="AG32" s="3">
         <v>9600</v>
       </c>
       <c r="AH32" s="3">
+        <v>9600</v>
+      </c>
+      <c r="AI32" s="3">
         <v>18700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>9600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>10400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>7300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>7000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>7500</v>
       </c>
-      <c r="AN32" s="3" t="s">
+      <c r="AO32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E33" s="3">
         <v>15000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>15100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>13100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>13900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>9000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>9800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>9700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>9000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>11100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>11500</v>
-      </c>
-      <c r="S33" s="3">
-        <v>10200</v>
       </c>
       <c r="T33" s="3">
         <v>10200</v>
       </c>
       <c r="U33" s="3">
+        <v>10200</v>
+      </c>
+      <c r="V33" s="3">
         <v>11200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>9600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>9000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>9700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>8400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>5100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>4500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>4000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>6100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>3000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>2900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1900</v>
       </c>
-      <c r="AN33" s="3" t="s">
+      <c r="AO33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3801,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E35" s="3">
         <v>15000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>15100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>13100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>13900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>9000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>9800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>9700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>9000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>11100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>11500</v>
-      </c>
-      <c r="S35" s="3">
-        <v>10200</v>
       </c>
       <c r="T35" s="3">
         <v>10200</v>
       </c>
       <c r="U35" s="3">
+        <v>10200</v>
+      </c>
+      <c r="V35" s="3">
         <v>11200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>9600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>9000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>9700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>8400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>5100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>4500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>4000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>6100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>3000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>2900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1900</v>
       </c>
-      <c r="AN35" s="3" t="s">
+      <c r="AO35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2" t="s">
+      <c r="AO38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4089,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,110 +4132,111 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>399300</v>
+      </c>
+      <c r="E41" s="3">
         <v>255600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>188900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>274600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>294000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>205300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>156700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>136500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>85200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>54000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>146200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>119300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>140400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>20000</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>14800</v>
       </c>
       <c r="R41" s="3">
         <v>14800</v>
       </c>
       <c r="S41" s="3">
+        <v>14800</v>
+      </c>
+      <c r="T41" s="3">
         <v>15000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>42900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>23700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>19700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>22700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>18500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>20100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>15600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>9600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>10500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>11100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>12300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>11600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>10400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>11000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>9800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>9600</v>
       </c>
-      <c r="AJ41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK41" s="3" t="s">
         <v>3</v>
       </c>
@@ -4162,13 +4249,16 @@
       <c r="AN41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -4204,68 +4294,68 @@
         <v>0</v>
       </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>60500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>22500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>236400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>299100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>140700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>300600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>289200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>295600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>128500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>185400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>184100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>165300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>104300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>44000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>67300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>26700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>24300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>29700</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>58900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>35500</v>
       </c>
-      <c r="AJ42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK42" s="3" t="s">
         <v>3</v>
       </c>
@@ -4278,8 +4368,11 @@
       <c r="AN42" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO42" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4298,18 +4391,18 @@
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3">
         <v>600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11600</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -4319,8 +4412,8 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -4394,16 +4487,19 @@
       <c r="AN43" s="3">
         <v>0</v>
       </c>
+      <c r="AO43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
         <v>3900</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>3</v>
+      <c r="E44" s="3">
+        <v>3900</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>3</v>
@@ -4435,8 +4531,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4510,50 +4606,53 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E45" s="3">
         <v>16700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>19000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>15100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>19500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>16700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>12200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>12300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>11200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10000</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -4626,50 +4725,53 @@
       <c r="AN45" s="3">
         <v>0</v>
       </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>440000</v>
+      </c>
+      <c r="E46" s="3">
         <v>301900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>227600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>310700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>348100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>239100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>189300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>169200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>119400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>72900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>162200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>139600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>160000</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -4742,50 +4844,53 @@
       <c r="AN46" s="3">
         <v>0</v>
       </c>
+      <c r="AO46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>230500</v>
+      </c>
+      <c r="E47" s="3">
         <v>230100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>232600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>228900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>213500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>223600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>208700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>207900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>202300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>208300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>206100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>208500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>255800</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -4858,100 +4963,103 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E48" s="3">
         <v>15100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>14900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>15100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>15500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>12200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3000</v>
-      </c>
-      <c r="AG48" s="3">
-        <v>2800</v>
       </c>
       <c r="AH48" s="3">
         <v>2800</v>
@@ -4959,8 +5067,8 @@
       <c r="AI48" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ48" s="3" t="s">
-        <v>3</v>
+      <c r="AJ48" s="3">
+        <v>2800</v>
       </c>
       <c r="AK48" s="3" t="s">
         <v>3</v>
@@ -4974,29 +5082,32 @@
       <c r="AN48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>42400</v>
+      </c>
+      <c r="E49" s="3">
         <v>42600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>43100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>40000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>41900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>42500</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
@@ -5090,8 +5201,11 @@
       <c r="AN49" s="3">
         <v>0</v>
       </c>
+      <c r="AO49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5320,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,97 +5439,100 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>90900</v>
+      </c>
+      <c r="E52" s="3">
         <v>96800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>87100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>86200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>85400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>88100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>70500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>53000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>50600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>52900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>50900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>50000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>49300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>13800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>14000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>12900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>12400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>9800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7200</v>
-      </c>
-      <c r="V52" s="3">
-        <v>7400</v>
       </c>
       <c r="W52" s="3">
         <v>7400</v>
       </c>
       <c r="X52" s="3">
+        <v>7400</v>
+      </c>
+      <c r="Y52" s="3">
         <v>6800</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>3600</v>
       </c>
       <c r="Z52" s="3">
         <v>3600</v>
       </c>
       <c r="AA52" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AB52" s="3">
         <v>4000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3600</v>
-      </c>
-      <c r="AF52" s="3">
-        <v>3700</v>
       </c>
       <c r="AG52" s="3">
         <v>3700</v>
@@ -5421,11 +5541,11 @@
         <v>3700</v>
       </c>
       <c r="AI52" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK52" s="3" t="s">
         <v>3</v>
       </c>
@@ -5438,8 +5558,11 @@
       <c r="AN52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,110 +5677,113 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3808500</v>
+      </c>
+      <c r="E54" s="3">
         <v>3606200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3389400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3388700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3349800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3206900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2560800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2438600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2324200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2226200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2272500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2227900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2245300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2123700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2009400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2154800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2122500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2055300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2169600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2151900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2091900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1876600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1879000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1822400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1507800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1427600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1311400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1234200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1123800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1105100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1072900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1067800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1017600</v>
       </c>
-      <c r="AJ54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5670,8 +5796,11 @@
       <c r="AN54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5841,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,110 +5884,111 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3292000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3093200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2912100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2940700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2891300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2761900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2186200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2100400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2005700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1896000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1968000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1934400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1944400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>300</v>
-      </c>
-      <c r="S57" s="3">
-        <v>500</v>
       </c>
       <c r="T57" s="3">
         <v>500</v>
       </c>
       <c r="U57" s="3">
+        <v>500</v>
+      </c>
+      <c r="V57" s="3">
         <v>800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2100</v>
-      </c>
-      <c r="AD57" s="3">
-        <v>2000</v>
       </c>
       <c r="AE57" s="3">
         <v>2000</v>
       </c>
       <c r="AF57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AG57" s="3">
         <v>1600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5870,50 +6001,53 @@
       <c r="AN57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>51600</v>
+      </c>
+      <c r="E58" s="3">
         <v>52000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>22500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>23100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>23600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>22000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>15000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10900</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -5986,8 +6120,11 @@
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6027,57 +6164,57 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3">
         <v>2400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>5100</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
@@ -6087,8 +6224,8 @@
       <c r="AI59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AJ59" s="3">
-        <v>0</v>
+      <c r="AJ59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AK59" s="3">
         <v>0</v>
@@ -6102,50 +6239,53 @@
       <c r="AN59" s="3">
         <v>0</v>
       </c>
+      <c r="AO59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3352600</v>
+      </c>
+      <c r="E60" s="3">
         <v>3153900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2942600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2971900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2924900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2793300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2195000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2107600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2012500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1916600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1973500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1938100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1957300</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -6218,49 +6358,52 @@
       <c r="AN60" s="3">
         <v>0</v>
       </c>
+      <c r="AO60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E61" s="3">
         <v>4700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>16400</v>
-      </c>
-      <c r="F61" s="3">
-        <v>16000</v>
       </c>
       <c r="G61" s="3">
         <v>16000</v>
       </c>
       <c r="H61" s="3">
+        <v>16000</v>
+      </c>
+      <c r="I61" s="3">
         <v>17900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>68200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>47900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>36700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>37900</v>
-      </c>
-      <c r="M61" s="3">
-        <v>37700</v>
       </c>
       <c r="N61" s="3">
         <v>37700</v>
       </c>
       <c r="O61" s="3">
+        <v>37700</v>
+      </c>
+      <c r="P61" s="3">
         <v>37200</v>
-      </c>
-      <c r="P61" s="3">
-        <v>12100</v>
       </c>
       <c r="Q61" s="3">
         <v>12100</v>
@@ -6284,16 +6427,16 @@
         <v>12100</v>
       </c>
       <c r="X61" s="3">
+        <v>12100</v>
+      </c>
+      <c r="Y61" s="3">
         <v>14000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>17500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>17400</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>15400</v>
       </c>
       <c r="AB61" s="3">
         <v>15400</v>
@@ -6314,14 +6457,14 @@
         <v>15400</v>
       </c>
       <c r="AH61" s="3">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>15400</v>
       </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
       <c r="AK61" s="3">
         <v>0</v>
       </c>
@@ -6334,50 +6477,53 @@
       <c r="AN61" s="3">
         <v>0</v>
       </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>38800</v>
+      </c>
+      <c r="E62" s="3">
         <v>45900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>35600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>20600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>39400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>40500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>17500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>15200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>15500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>18400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16300</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
@@ -6450,8 +6596,11 @@
       <c r="AN62" s="3">
         <v>0</v>
       </c>
+      <c r="AO62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6715,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6834,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,110 +6953,113 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3399600</v>
+      </c>
+      <c r="E66" s="3">
         <v>3204500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2994700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3008600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2980200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2851800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2280700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2170700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2064800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1971300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2029600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1990400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2010800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1899600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1795400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1947500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1921000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1857400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1980500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1974600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1924800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1717300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1729700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1680300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1371800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1294300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1183600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1111000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1005200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>990500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>966200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>980800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>934200</v>
       </c>
-      <c r="AJ66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6914,8 +7072,11 @@
       <c r="AN66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7117,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7234,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7353,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7472,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,110 +7591,113 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>302800</v>
+      </c>
+      <c r="E72" s="3">
         <v>292700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>274000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>261100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>249900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>242900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>233000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>225800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>218700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>213300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>206000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>197500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>191100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>182400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>174900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>164800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>153900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>144500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>135900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>125400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>115800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>106900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>97600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>89200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>84400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>81600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>77100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>72900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>68900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>65700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>62500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>59300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>56200</v>
       </c>
-      <c r="AJ72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK72" s="3" t="s">
         <v>3</v>
       </c>
@@ -7536,8 +7710,11 @@
       <c r="AN72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +7829,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +7948,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,110 +8067,113 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>408900</v>
+      </c>
+      <c r="E76" s="3">
         <v>401800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>394800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>380000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>369600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>355100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>280100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>267900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>259500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>254900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>242900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>237400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>234500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>224000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>214000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>207300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>201500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>197900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>189100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>177200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>167000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>159300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>149400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>142100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>136100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>133300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>127800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>123100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>118600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>114600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>106700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>87000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>83400</v>
       </c>
-      <c r="AJ76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK76" s="3" t="s">
         <v>3</v>
       </c>
@@ -8000,8 +8186,11 @@
       <c r="AN76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8305,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2" t="s">
+      <c r="AO80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E81" s="3">
         <v>15000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>15100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>13100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>13900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>9000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>9800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>9700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>9000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>11100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>11500</v>
-      </c>
-      <c r="S81" s="3">
-        <v>10200</v>
       </c>
       <c r="T81" s="3">
         <v>10200</v>
       </c>
       <c r="U81" s="3">
+        <v>10200</v>
+      </c>
+      <c r="V81" s="3">
         <v>11200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>9600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>9000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>9700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>8400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>5100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>4500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>4000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>6100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>3000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>2900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1900</v>
       </c>
-      <c r="AN81" s="3" t="s">
+      <c r="AO81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,34 +8593,35 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>600</v>
+      </c>
+      <c r="E83" s="3">
         <v>1700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-100</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
       <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
         <v>300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>-200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>-100</v>
-      </c>
-      <c r="K83" s="3">
-        <v>300</v>
       </c>
       <c r="L83" s="3">
         <v>300</v>
@@ -8431,49 +8630,49 @@
         <v>300</v>
       </c>
       <c r="N83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="O83" s="3">
         <v>400</v>
       </c>
       <c r="P83" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q83" s="3">
         <v>-700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>300</v>
-      </c>
-      <c r="R83" s="3">
-        <v>400</v>
       </c>
       <c r="S83" s="3">
         <v>400</v>
       </c>
       <c r="T83" s="3">
+        <v>400</v>
+      </c>
+      <c r="U83" s="3">
         <v>-500</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
       <c r="V83" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="W83" s="3">
         <v>500</v>
       </c>
       <c r="X83" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y83" s="3">
         <v>-600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>500</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>300</v>
       </c>
       <c r="AC83" s="3">
         <v>300</v>
@@ -8488,31 +8687,34 @@
         <v>300</v>
       </c>
       <c r="AG83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH83" s="3">
         <v>200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>300</v>
       </c>
-      <c r="AJ83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK83" s="3">
+      <c r="AK83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL83" s="3">
         <v>200</v>
       </c>
-      <c r="AL83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +8829,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +8948,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9067,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9186,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9305,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E89" s="3">
         <v>18500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>32900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>22600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>25900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>12900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>22500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>8400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>10400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>15800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>20300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>9200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>29500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>26400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>21500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>54600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>41300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-30100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>8200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-14800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-21500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>10400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>15100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>12900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>6800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>4700</v>
       </c>
-      <c r="AL89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,86 +9469,87 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3">
         <v>400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-2300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-700</v>
       </c>
       <c r="R91" s="3">
         <v>-700</v>
       </c>
       <c r="S91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-400</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X91" s="3">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y91" s="3">
         <v>100</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
@@ -9338,35 +9559,38 @@
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-700</v>
-      </c>
-      <c r="AI91" s="3">
-        <v>-400</v>
       </c>
       <c r="AJ91" s="3">
         <v>-400</v>
       </c>
       <c r="AK91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-300</v>
       </c>
-      <c r="AL91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9705,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +9824,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-72100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-141400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-88100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-60300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-61100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-63100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-83700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-65500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-57600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-39100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-26300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-58700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-68000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-77700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-108800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>56100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-45900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-14500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-85300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-92600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-86000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-34000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-249500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-16000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-57300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-81700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-42500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-6400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-43400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-33800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-32000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-12000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-16700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-32300</v>
       </c>
-      <c r="AL94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,8 +9988,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9767,7 +10001,7 @@
         <v>2000</v>
       </c>
       <c r="F96" s="3">
-        <v>1700</v>
+        <v>2000</v>
       </c>
       <c r="G96" s="3">
         <v>1700</v>
@@ -9776,10 +10010,10 @@
         <v>1700</v>
       </c>
       <c r="I96" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J96" s="3">
         <v>1400</v>
-      </c>
-      <c r="J96" s="3">
-        <v>1100</v>
       </c>
       <c r="K96" s="3">
         <v>1100</v>
@@ -9791,25 +10025,25 @@
         <v>1100</v>
       </c>
       <c r="N96" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O96" s="3">
         <v>800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>900</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-800</v>
       </c>
       <c r="Q96" s="3">
         <v>-800</v>
       </c>
       <c r="R96" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="S96" s="3">
         <v>-700</v>
       </c>
       <c r="T96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="U96" s="3">
         <v>0</v>
@@ -9871,8 +10105,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10224,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10343,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,124 +10462,130 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>194000</v>
+      </c>
+      <c r="E100" s="3">
         <v>189700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-30600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>45100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>127200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>85800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>104400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>103900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>92300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-59200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>30600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-22700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>108300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>105300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-151900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>25600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>65100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-124300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>54400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>209100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>48700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>304400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>73000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>109700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>72100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>105200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>8300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>27000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>3000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>33300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-10600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>22700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>16600</v>
       </c>
-      <c r="AL100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10376,8 +10625,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10451,120 +10700,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>143700</v>
+      </c>
+      <c r="E102" s="3">
         <v>66700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-85700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-19400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>88700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>48600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>20200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>51300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>31200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-92200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>26800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-21000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>60000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>43400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-213800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-62900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>130400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-140600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>15300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-9400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>171100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-58600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>5800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>24800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>60000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>59700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-24500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>41200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>3600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-28000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>16400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-9700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>12700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-10900</v>
       </c>
-      <c r="AL102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
